--- a/CornBelters/Scouting Reports/Tables.xlsx
+++ b/CornBelters/Scouting Reports/Tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77e568506d41aebf/Cornbelters/Scouting Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Cornbelters\Kernelytics-Projects\CornBelters\Scouting Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1537" documentId="8_{EB96EC1F-B635-4C79-A011-C477669E0912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD306DDE-F13B-47FE-A863-6CC940980CCE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D24800-FE0D-4A0E-B2FC-BCBC6250C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="6" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitchers (Spring Stats)" sheetId="1" state="hidden" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="LafayetteSpringHitting" sheetId="6" r:id="rId6"/>
     <sheet name="REXSpringPitching" sheetId="10" r:id="rId7"/>
     <sheet name="REXSpringHitting" sheetId="9" r:id="rId8"/>
+    <sheet name="ChillicotheSpringPitching" sheetId="12" r:id="rId9"/>
+    <sheet name="ChillicotheSpringHitting" sheetId="13" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="319">
   <si>
     <t>#</t>
   </si>
@@ -768,33 +770,250 @@
     <t>SP 5/31, 96</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Swanson</t>
-  </si>
-  <si>
-    <t>Guadamuz</t>
-  </si>
-  <si>
-    <t>Ray</t>
-  </si>
-  <si>
-    <t>Marrs</t>
-  </si>
-  <si>
-    <t>Contreras</t>
+    <t>Alex Bemis</t>
+  </si>
+  <si>
+    <t>Gannon (NCAA D2)</t>
+  </si>
+  <si>
+    <t>Kale Wemer</t>
+  </si>
+  <si>
+    <t>RP 6/3, 25</t>
+  </si>
+  <si>
+    <t>Cam Gravelle</t>
+  </si>
+  <si>
+    <t>Toledo (NCAA D1)</t>
+  </si>
+  <si>
+    <t>K%</t>
+  </si>
+  <si>
+    <t>Zack Henderson</t>
+  </si>
+  <si>
+    <t>Zach?</t>
+  </si>
+  <si>
+    <t>Jacob Buysse</t>
+  </si>
+  <si>
+    <t>West Virginia State (NCAA D2)</t>
+  </si>
+  <si>
+    <t>Mitchel Szymczak</t>
+  </si>
+  <si>
+    <t>Buysee?</t>
+  </si>
+  <si>
+    <t>Lake Erie (NCAA D2)</t>
+  </si>
+  <si>
+    <t>Micah Geise</t>
+  </si>
+  <si>
+    <t>BB%</t>
+  </si>
+  <si>
+    <t>Carson Cox</t>
+  </si>
+  <si>
+    <t>Tyler Mendez</t>
+  </si>
+  <si>
+    <t>Brookdale CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/4, 47</t>
+  </si>
+  <si>
+    <t>Matt Moscarino</t>
+  </si>
+  <si>
+    <t>Baldwin Wallace (NCAA D3)</t>
+  </si>
+  <si>
+    <t>SP 6/3, 96</t>
+  </si>
+  <si>
+    <t>CJ Richmond</t>
+  </si>
+  <si>
+    <t>Trent Hedges</t>
+  </si>
+  <si>
+    <t>Tiffin (NCAA D2)</t>
+  </si>
+  <si>
+    <t>CP 6/3, 15</t>
+  </si>
+  <si>
+    <t>Colin West</t>
+  </si>
+  <si>
+    <t>Dylan Lloyd</t>
+  </si>
+  <si>
+    <t>Hanover (NCAA D3)</t>
+  </si>
+  <si>
+    <t>SP 5/31, 95</t>
+  </si>
+  <si>
+    <t>Mason McManus</t>
+  </si>
+  <si>
+    <t>Erskine (NCAA D2)</t>
+  </si>
+  <si>
+    <t>Will Rodriguez</t>
+  </si>
+  <si>
+    <t>RP 6/5, 8</t>
+  </si>
+  <si>
+    <t>Michael Patellis</t>
+  </si>
+  <si>
+    <t>Jackson Boles</t>
+  </si>
+  <si>
+    <t>Cuyahoga CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>AJ Dallmayer</t>
+  </si>
+  <si>
+    <t>RP 6/1, 54</t>
+  </si>
+  <si>
+    <t>CJ Carmichael</t>
+  </si>
+  <si>
+    <t>Frostburg State (NCAA D2)</t>
+  </si>
+  <si>
+    <t>Zane Vitense</t>
+  </si>
+  <si>
+    <t>Ohio Wesleyan (NCAA D3)</t>
+  </si>
+  <si>
+    <t>RP 6/5, 25</t>
+  </si>
+  <si>
+    <t>Nate Hill</t>
+  </si>
+  <si>
+    <t>2024 stats</t>
+  </si>
+  <si>
+    <t>Gavin Beuter</t>
+  </si>
+  <si>
+    <t>SP 5/30, 75</t>
+  </si>
+  <si>
+    <t>Luke Walter</t>
+  </si>
+  <si>
+    <t>Otterbein (NCAA D3)</t>
+  </si>
+  <si>
+    <t>SP 6/4, 70</t>
+  </si>
+  <si>
+    <t>Tyler Stone</t>
+  </si>
+  <si>
+    <t>Kean (NCAA D3)</t>
+  </si>
+  <si>
+    <t>Branin Seibert</t>
+  </si>
+  <si>
+    <t>RP 6/5, 21</t>
+  </si>
+  <si>
+    <t>JT Fabian</t>
+  </si>
+  <si>
+    <t>SP 6/1, 62</t>
+  </si>
+  <si>
+    <t>Cal Chase</t>
+  </si>
+  <si>
+    <t>Justin Teixiera</t>
+  </si>
+  <si>
+    <t>AJ McAninch</t>
+  </si>
+  <si>
+    <t>Marshall (NCAA D1)</t>
+  </si>
+  <si>
+    <t>RP 6/4, 29</t>
+  </si>
+  <si>
+    <t>Justin Gorski</t>
+  </si>
+  <si>
+    <t>Miami (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Vince Waterman</t>
+  </si>
+  <si>
+    <t>Zach Neville</t>
+  </si>
+  <si>
+    <t>Alex Caudill</t>
+  </si>
+  <si>
+    <t>SP 6/5, 84</t>
+  </si>
+  <si>
+    <t>Mahoney Daunic</t>
+  </si>
+  <si>
+    <t>Denison (NCAA D3)</t>
+  </si>
+  <si>
+    <t>Christian Pareja</t>
+  </si>
+  <si>
+    <t>Moscarino</t>
+  </si>
+  <si>
+    <t>Lloyd</t>
+  </si>
+  <si>
+    <t>Beuter</t>
+  </si>
+  <si>
+    <t>Walter</t>
+  </si>
+  <si>
+    <t>Fabian</t>
+  </si>
+  <si>
+    <t>Caudill</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode=".000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,8 +1029,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -836,6 +1062,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -846,10 +1078,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -912,11 +1145,211 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="127">
+  <dxfs count="154">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -943,6 +1376,42 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -968,81 +1437,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1497,57 +1891,100 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:O19" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="151"/>
     <tableColumn id="2" xr3:uid="{4B207364-C81F-4AB0-A7A1-6179ED226E0C}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="122"/>
-    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="121"/>
-    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="120"/>
-    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="119"/>
-    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="118"/>
-    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="117"/>
-    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="116"/>
-    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="115"/>
-    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="114"/>
-    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="113"/>
-    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="150"/>
+    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="149"/>
+    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="148"/>
+    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="147"/>
+    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="146"/>
+    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="145"/>
+    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="144"/>
+    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="143"/>
+    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="142"/>
+    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="141"/>
+    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="140"/>
+    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="139"/>
     <tableColumn id="15" xr3:uid="{6F146679-03A5-4608-8323-E75FAFF903E6}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0843ECD0-6996-45AC-A9A9-494D040880A6}" name="Table2671011" displayName="Table2671011" ref="A1:L20" totalsRowShown="0" headerRowDxfId="6" dataDxfId="26">
+  <autoFilter ref="A1:L20" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{DDD953FD-5011-49C3-9230-44FD2E664EE4}" name="#" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{C5B71AC5-1440-4ADE-BA98-FB907CC5B174}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{CE3006DC-DE43-451A-BE91-7DA1A81785E0}" name="Throws" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{B5E7AA9B-A56D-4805-BB36-39D375AE9533}" name="School" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{E42FD4B5-177E-4DFE-A2F5-247966E47C02}" name="ERA" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{33B5FF3A-1C37-4003-B2C4-C7CA9DF6D068}" name="IP" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{16EB2C0E-C141-4947-83DF-FAD21AE3D884}" name="H" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{998831EB-F6EF-4D4E-ACED-441C6839236E}" name="ER" dataDxfId="19"/>
+    <tableColumn id="11" xr3:uid="{56149B59-21AA-43DC-A628-D4B816C4BD8D}" name="HR" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{172AC206-5FBE-4E78-B1E1-C9DA83788B1B}" name="BB" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{E8C6BF8F-17A6-4CA1-B5EE-4010D8E6E237}" name="SO" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{411967A6-2B93-4978-A8B5-D67AEDB498DB}" name="Last PL Outing, NP" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{20B053F4-F88D-4429-AA41-68D802CD1DF8}" name="Table1458912" displayName="Table1458912" ref="A1:M19" totalsRowShown="0" headerRowDxfId="3" dataDxfId="14">
+  <autoFilter ref="A1:M19" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{41FBD773-60D6-4C44-A4FB-F9B3AC2FF215}" name="#" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{7283EBB3-ECFD-4150-B86E-E64B8998B944}" name="Name"/>
+    <tableColumn id="5" xr3:uid="{754D84E1-E5E5-4628-BE76-6FC3F40A499D}" name="School" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{831F66A7-878D-4156-94CB-7A6FAC523764}" name="PA" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{3415C3C4-46AA-480E-9A6C-26B96A96F229}" name="H" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{79AF8C5A-6B40-47EB-AE42-4B6470FC7335}" name="HR" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{7199D5C9-AF2B-4B9A-B085-659C519522A1}" name="BB" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{951AAA57-6EF3-4291-812C-F7231AB5B201}" name="SO" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{C58BF7E3-497D-4DA5-A7AD-A0DA6D6F35FE}" name="AVG" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{E7A8FCAD-07A0-4F17-BD83-CD5B529C19EF}" name="OBP" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{6CC324F1-66DA-48AB-8C9A-BDD8D93CC895}" name="SB" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{DE70BA46-0B42-4F84-BC0E-499D6EF099B4}" name="K%" dataDxfId="1">
+      <calculatedColumnFormula>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{6D28691B-C12C-444A-8445-978CAEDE2F9E}" name="BB%" dataDxfId="0" dataCellStyle="Percent">
+      <calculatedColumnFormula>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="111" dataDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137">
   <autoFilter ref="A1:T20" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="136"/>
     <tableColumn id="2" xr3:uid="{1E71FAB3-5F80-433A-9CF9-976B18697772}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="107"/>
-    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="106"/>
-    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="105"/>
-    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="104"/>
-    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="103"/>
-    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="102"/>
-    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="101"/>
-    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="100"/>
-    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="99"/>
-    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="98"/>
-    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="97"/>
-    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="96"/>
-    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="95"/>
-    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="94"/>
-    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="93"/>
-    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="135"/>
+    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="134"/>
+    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="133"/>
+    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="132"/>
+    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="131"/>
+    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="130"/>
+    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="129"/>
+    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="128"/>
+    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="127"/>
+    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="126"/>
+    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="125"/>
+    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="124"/>
+    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="123"/>
+    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="122"/>
+    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="121"/>
+    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="120"/>
+    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="119"/>
     <tableColumn id="20" xr3:uid="{63D55BB7-68A9-437C-9C45-35CEA0F3FE2B}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1555,26 +1992,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
   <autoFilter ref="A32:R51" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="89"/>
+    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="116"/>
     <tableColumn id="2" xr3:uid="{ABA958D3-F28A-4755-9648-E1D80184B0D4}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="87"/>
-    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="86"/>
-    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="85"/>
-    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="83"/>
-    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="82"/>
-    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="81"/>
-    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="80"/>
-    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="79"/>
-    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="78"/>
-    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="77"/>
-    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="76"/>
-    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="75"/>
-    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="115"/>
+    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="114"/>
+    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="112"/>
+    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="111"/>
+    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="110"/>
+    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="109"/>
+    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="108"/>
+    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="107"/>
+    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="106"/>
+    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="105"/>
+    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="104"/>
+    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="103"/>
+    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="102"/>
+    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="101"/>
     <tableColumn id="20" xr3:uid="{D6FD6B3E-0891-49E1-9B8B-AEF67C143114}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1582,20 +2019,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="98"/>
     <tableColumn id="2" xr3:uid="{516EEF33-51BA-4936-98F6-F4E8C86D9AB9}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="68"/>
-    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="67"/>
-    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="66"/>
-    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="63"/>
-    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="93"/>
+    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="92"/>
+    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="91"/>
+    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="90"/>
+    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="89"/>
     <tableColumn id="15" xr3:uid="{2568029A-6AFC-43E6-B446-46528B9915F4}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1603,20 +2040,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
   <autoFilter ref="A1:L20" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="86"/>
     <tableColumn id="2" xr3:uid="{984187B9-FA1E-4DBC-B804-6E035D1B61A2}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="55"/>
-    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="54"/>
-    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="53"/>
-    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="52"/>
-    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="51"/>
-    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="84"/>
+    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="83"/>
+    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="82"/>
+    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="80"/>
+    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="79"/>
+    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="78"/>
+    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="77"/>
     <tableColumn id="20" xr3:uid="{9348918D-5ECB-448B-A085-487540424189}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1624,82 +2061,82 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
   <autoFilter ref="A1:K19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="74"/>
     <tableColumn id="2" xr3:uid="{FD907DA6-0C2B-490D-862C-004A3C98FA20}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="41"/>
-    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="39"/>
-    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="69"/>
+    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="68"/>
+    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="67"/>
+    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="66"/>
+    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A1:K17" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="62"/>
     <tableColumn id="2" xr3:uid="{A108195E-3469-4ACD-AA5B-AAB9CB14C59B}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="30"/>
-    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="29"/>
-    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="28"/>
-    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="59"/>
+    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="57"/>
+    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="56"/>
+    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="55"/>
+    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="54"/>
+    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="1" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="50"/>
     <tableColumn id="2" xr3:uid="{6377AB1F-C5EE-4699-A482-9F1094364D72}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:L15" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="37"/>
     <tableColumn id="2" xr3:uid="{F0F04FB6-1130-4097-843F-75D32B7FDEAA}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="22"/>
-    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="18"/>
-    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="17"/>
-    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="16"/>
-    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="36"/>
+    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="34"/>
+    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="29"/>
+    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2791,6 +3228,850 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86E2FF5-2AAA-4871-BF7B-8F1A7A76F7CD}">
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" style="30"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="1">
+        <v>191</v>
+      </c>
+      <c r="E2" s="1">
+        <v>52</v>
+      </c>
+      <c r="F2" s="1">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1">
+        <v>29</v>
+      </c>
+      <c r="I2" s="28">
+        <v>0.311</v>
+      </c>
+      <c r="J2" s="28">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="K2" s="6">
+        <v>14</v>
+      </c>
+      <c r="L2" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.15183246073298429</v>
+      </c>
+      <c r="M2" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.12041884816753927</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" s="11">
+        <v>82</v>
+      </c>
+      <c r="E3" s="11">
+        <v>15</v>
+      </c>
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11">
+        <v>13</v>
+      </c>
+      <c r="I3" s="29">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0.247</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.15853658536585366</v>
+      </c>
+      <c r="M3" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>4.878048780487805E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="11">
+        <v>44</v>
+      </c>
+      <c r="E4" s="11">
+        <v>11</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
+        <v>6</v>
+      </c>
+      <c r="H4" s="11">
+        <v>8</v>
+      </c>
+      <c r="I4" s="29">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="J4" s="29">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="K4" s="11">
+        <v>3</v>
+      </c>
+      <c r="L4" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="M4" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="N4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="1">
+        <v>35</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>15</v>
+      </c>
+      <c r="I5" s="28">
+        <v>0.121</v>
+      </c>
+      <c r="J5" s="28">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="M5" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>5.7142857142857141E-2</v>
+      </c>
+      <c r="N5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="11">
+        <v>175</v>
+      </c>
+      <c r="E6" s="11">
+        <v>32</v>
+      </c>
+      <c r="F6" s="11">
+        <v>6</v>
+      </c>
+      <c r="G6" s="11">
+        <v>25</v>
+      </c>
+      <c r="H6" s="11">
+        <v>28</v>
+      </c>
+      <c r="I6" s="29">
+        <v>0.218</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="K6" s="11">
+        <v>6</v>
+      </c>
+      <c r="L6" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.16</v>
+      </c>
+      <c r="M6" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="1">
+        <v>148</v>
+      </c>
+      <c r="E7" s="1">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1">
+        <v>38</v>
+      </c>
+      <c r="I7" s="28">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="J7" s="28">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="K7" s="6">
+        <v>10</v>
+      </c>
+      <c r="L7" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.25675675675675674</v>
+      </c>
+      <c r="M7" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.1554054054054054</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="1">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+      <c r="I8" s="28">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="J8" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="M8" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="1">
+        <v>140</v>
+      </c>
+      <c r="E9" s="1">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1">
+        <v>38</v>
+      </c>
+      <c r="I9" s="28">
+        <v>0.221</v>
+      </c>
+      <c r="J9" s="28">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="K9" s="6">
+        <v>2</v>
+      </c>
+      <c r="L9" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.27142857142857141</v>
+      </c>
+      <c r="M9" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.12142857142857143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D10" s="1">
+        <v>137</v>
+      </c>
+      <c r="E10" s="1">
+        <v>39</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1">
+        <v>12</v>
+      </c>
+      <c r="I10" s="28">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="J10" s="28">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="K10" s="6">
+        <v>7</v>
+      </c>
+      <c r="L10" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>8.7591240875912413E-2</v>
+      </c>
+      <c r="M10" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.13868613138686131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" s="1">
+        <v>86</v>
+      </c>
+      <c r="E11" s="1">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>8</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="29">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J11" s="29">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="M11" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>9.3023255813953487E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="1">
+        <v>37</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>19</v>
+      </c>
+      <c r="I12" s="28">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="J12" s="28">
+        <v>0.189</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.51351351351351349</v>
+      </c>
+      <c r="M12" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>8.1081081081081086E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" t="s">
+        <v>278</v>
+      </c>
+      <c r="D13" s="11">
+        <v>195</v>
+      </c>
+      <c r="E13" s="11">
+        <v>64</v>
+      </c>
+      <c r="F13" s="11">
+        <v>10</v>
+      </c>
+      <c r="G13" s="11">
+        <v>26</v>
+      </c>
+      <c r="H13" s="11">
+        <v>15</v>
+      </c>
+      <c r="I13" s="29">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J13" s="29">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="K13" s="11">
+        <v>39</v>
+      </c>
+      <c r="L13" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="M13" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" s="1">
+        <v>188</v>
+      </c>
+      <c r="E14" s="1">
+        <v>47</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1">
+        <v>24</v>
+      </c>
+      <c r="H14" s="1">
+        <v>23</v>
+      </c>
+      <c r="I14" s="28">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="J14" s="28">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="K14" s="6">
+        <v>15</v>
+      </c>
+      <c r="L14" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.12234042553191489</v>
+      </c>
+      <c r="M14" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.1276595744680851</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="1">
+        <v>121</v>
+      </c>
+      <c r="E15" s="1">
+        <v>37</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>11</v>
+      </c>
+      <c r="I15" s="28">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="J15" s="28">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="M15" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>6.6115702479338845E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="1">
+        <v>36</v>
+      </c>
+      <c r="E16" s="1">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="28">
+        <v>0.121</v>
+      </c>
+      <c r="J16" s="28">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="M16" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" s="1">
+        <v>241</v>
+      </c>
+      <c r="E17" s="1">
+        <v>66</v>
+      </c>
+      <c r="F17" s="1">
+        <v>4</v>
+      </c>
+      <c r="G17" s="1">
+        <v>32</v>
+      </c>
+      <c r="H17" s="1">
+        <v>23</v>
+      </c>
+      <c r="I17" s="28">
+        <v>0.34</v>
+      </c>
+      <c r="J17" s="28">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="K17" s="6">
+        <v>10</v>
+      </c>
+      <c r="L17" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>9.5435684647302899E-2</v>
+      </c>
+      <c r="M17" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.13278008298755187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D18" s="1">
+        <v>230</v>
+      </c>
+      <c r="E18" s="1">
+        <v>51</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>35</v>
+      </c>
+      <c r="H18" s="1">
+        <v>27</v>
+      </c>
+      <c r="I18" s="28">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="J18" s="28">
+        <v>0.42</v>
+      </c>
+      <c r="K18" s="6">
+        <v>14</v>
+      </c>
+      <c r="L18" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.11739130434782609</v>
+      </c>
+      <c r="M18" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.15217391304347827</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D19" s="1">
+        <v>29</v>
+      </c>
+      <c r="E19" s="1">
+        <v>4</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1">
+        <v>8</v>
+      </c>
+      <c r="I19" s="28">
+        <v>0.19</v>
+      </c>
+      <c r="J19" s="28">
+        <v>0.32</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1</v>
+      </c>
+      <c r="L19" s="34">
+        <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="M19" s="35">
+        <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
+        <v>0.13793103448275862</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F12F20D-5084-4348-9FD5-CBEE88AF2FDD}">
   <dimension ref="A1:T53"/>
@@ -7851,12 +9132,7 @@
       <c r="L6" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="P6" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q6" s="23">
-        <v>45806</v>
-      </c>
+      <c r="Q6" s="23"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -7895,12 +9171,7 @@
       <c r="L7" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P7" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q7" s="23">
-        <v>45807</v>
-      </c>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -7939,12 +9210,7 @@
       <c r="L8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="P8" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q8" s="23">
-        <v>45808</v>
-      </c>
+      <c r="Q8" s="23"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -7983,12 +9249,7 @@
       <c r="L9" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="P9" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q9" s="23">
-        <v>45809</v>
-      </c>
+      <c r="Q9" s="23"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -8027,12 +9288,7 @@
       <c r="L10" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="P10" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q10" s="23">
-        <v>45811</v>
-      </c>
+      <c r="Q10" s="23"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -8071,12 +9327,7 @@
       <c r="L11" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="P11" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q11" s="23">
-        <v>45812</v>
-      </c>
+      <c r="Q11" s="23"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -8955,4 +10206,824 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E67C1EB-ED46-48E3-8D94-E34847913498}">
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="11">
+        <v>4.45</v>
+      </c>
+      <c r="F3" s="11">
+        <v>32.1</v>
+      </c>
+      <c r="G3" s="11">
+        <v>27</v>
+      </c>
+      <c r="H3" s="11">
+        <v>16</v>
+      </c>
+      <c r="I3" s="11">
+        <v>5</v>
+      </c>
+      <c r="J3" s="11">
+        <v>19</v>
+      </c>
+      <c r="K3" s="11">
+        <v>41</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="P3" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q3" s="23">
+        <v>45807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.61</v>
+      </c>
+      <c r="F4" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>39</v>
+      </c>
+      <c r="H4" s="1">
+        <v>14</v>
+      </c>
+      <c r="I4" s="1">
+        <v>3</v>
+      </c>
+      <c r="J4" s="1">
+        <v>13</v>
+      </c>
+      <c r="K4" s="1">
+        <v>35</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="P4" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>45808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5.52</v>
+      </c>
+      <c r="F5" s="16">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>7</v>
+      </c>
+      <c r="K5" s="1">
+        <v>22</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="P5" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.24</v>
+      </c>
+      <c r="F6" s="16">
+        <v>46</v>
+      </c>
+      <c r="G6" s="1">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1">
+        <v>37</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>28</v>
+      </c>
+      <c r="K6" s="1">
+        <v>45</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="P6" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>45811</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12.32</v>
+      </c>
+      <c r="F7" s="16">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <v>33</v>
+      </c>
+      <c r="H7" s="1">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3</v>
+      </c>
+      <c r="J7" s="1">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P7" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>45812</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="1">
+        <v>17.47</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7</v>
+      </c>
+      <c r="H8" s="1">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>12</v>
+      </c>
+      <c r="K8" s="1">
+        <v>7</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="P8" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>45813</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="5">
+        <v>24.75</v>
+      </c>
+      <c r="F9" s="16">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q9" s="23"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="11">
+        <v>6.23</v>
+      </c>
+      <c r="F10" s="17">
+        <v>30.1</v>
+      </c>
+      <c r="G10" s="11">
+        <v>41</v>
+      </c>
+      <c r="H10" s="11">
+        <v>21</v>
+      </c>
+      <c r="I10" s="11">
+        <v>5</v>
+      </c>
+      <c r="J10" s="11">
+        <v>10</v>
+      </c>
+      <c r="K10" s="11">
+        <v>21</v>
+      </c>
+      <c r="L10" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q10" s="23"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4.63</v>
+      </c>
+      <c r="F11" s="16">
+        <v>35</v>
+      </c>
+      <c r="G11" s="1">
+        <v>41</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>26</v>
+      </c>
+      <c r="K11" s="1">
+        <v>22</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q11" s="23"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5.67</v>
+      </c>
+      <c r="F12" s="1">
+        <v>60.1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>63</v>
+      </c>
+      <c r="H12" s="1">
+        <v>38</v>
+      </c>
+      <c r="I12" s="1">
+        <v>13</v>
+      </c>
+      <c r="J12" s="1">
+        <v>51</v>
+      </c>
+      <c r="K12" s="1">
+        <v>64</v>
+      </c>
+      <c r="L12" s="24" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F13" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>42</v>
+      </c>
+      <c r="H13" s="1">
+        <v>28</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1">
+        <v>45</v>
+      </c>
+      <c r="K13" s="1">
+        <v>44</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5.66</v>
+      </c>
+      <c r="F14" s="16">
+        <v>20.2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>19</v>
+      </c>
+      <c r="H14" s="1">
+        <v>13</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
+        <v>14</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>301</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1">
+        <v>4</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>308</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="1">
+        <v>4.08</v>
+      </c>
+      <c r="F18" s="16">
+        <v>64</v>
+      </c>
+      <c r="G18" s="1">
+        <v>38</v>
+      </c>
+      <c r="H18" s="1">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>48</v>
+      </c>
+      <c r="K18" s="1">
+        <v>89</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>310</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="E19" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="F19" s="16">
+        <v>5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="1">
+        <v>3</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>76</v>
+      </c>
+      <c r="B20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="F20" s="1">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="G20" s="1">
+        <v>65</v>
+      </c>
+      <c r="H20" s="1">
+        <v>23</v>
+      </c>
+      <c r="I20" s="1">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
+        <v>30</v>
+      </c>
+      <c r="K20" s="1">
+        <v>47</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/CornBelters/Scouting Reports/Tables.xlsx
+++ b/CornBelters/Scouting Reports/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Cornbelters\Kernelytics-Projects\CornBelters\Scouting Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D24800-FE0D-4A0E-B2FC-BCBC6250C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03BEFDC-C9A0-4B99-BE0E-5B2095D5E403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="8" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="10" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitchers (Spring Stats)" sheetId="1" state="hidden" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="REXSpringHitting" sheetId="9" r:id="rId8"/>
     <sheet name="ChillicotheSpringPitching" sheetId="12" r:id="rId9"/>
     <sheet name="ChillicotheSpringHitting" sheetId="13" r:id="rId10"/>
+    <sheet name="ClintonSpringPitching" sheetId="14" r:id="rId11"/>
+    <sheet name="ClintonSpringHitting" sheetId="15" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="408">
   <si>
     <t>#</t>
   </si>
@@ -1002,6 +1004,273 @@
   </si>
   <si>
     <t>Caudill</t>
+  </si>
+  <si>
+    <t>Blake Timmons</t>
+  </si>
+  <si>
+    <t>Danny Gavin</t>
+  </si>
+  <si>
+    <t>North Dakota State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Gustavus Adolphus (NCAA D3)</t>
+  </si>
+  <si>
+    <t>JC Dermody</t>
+  </si>
+  <si>
+    <t>Wichita State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>SP 6/5, 60</t>
+  </si>
+  <si>
+    <t>Jackson Bruno</t>
+  </si>
+  <si>
+    <t>Jamie Rasmussen</t>
+  </si>
+  <si>
+    <t>Jake Weissenberger</t>
+  </si>
+  <si>
+    <t>Colin Coonradt</t>
+  </si>
+  <si>
+    <t>Alex Schimmel</t>
+  </si>
+  <si>
+    <t>James Hackett</t>
+  </si>
+  <si>
+    <t>Camden Clewett</t>
+  </si>
+  <si>
+    <t>Noah Thein</t>
+  </si>
+  <si>
+    <t>Brody Meyers</t>
+  </si>
+  <si>
+    <t>Hunter Dierksen</t>
+  </si>
+  <si>
+    <t>Garret Siemsen</t>
+  </si>
+  <si>
+    <t>Brayden Mulkey</t>
+  </si>
+  <si>
+    <t>Joey Hagen</t>
+  </si>
+  <si>
+    <t>Nick Venteicher</t>
+  </si>
+  <si>
+    <t>Brytton Clements</t>
+  </si>
+  <si>
+    <t>Bryk Barnard</t>
+  </si>
+  <si>
+    <t>Payton Hodges</t>
+  </si>
+  <si>
+    <t>Jimmy Burke</t>
+  </si>
+  <si>
+    <t>Sam Wiese</t>
+  </si>
+  <si>
+    <t>Ethan Dorka</t>
+  </si>
+  <si>
+    <t>Drew Terpins</t>
+  </si>
+  <si>
+    <t>Brett White</t>
+  </si>
+  <si>
+    <t>Cole Bormann</t>
+  </si>
+  <si>
+    <t>Max Burt</t>
+  </si>
+  <si>
+    <t>Nick Baffa</t>
+  </si>
+  <si>
+    <t>Chance Key</t>
+  </si>
+  <si>
+    <t>Matthew Maize</t>
+  </si>
+  <si>
+    <t>Austin Mallee</t>
+  </si>
+  <si>
+    <t>Will Schufreider</t>
+  </si>
+  <si>
+    <t>Tanner Duncan</t>
+  </si>
+  <si>
+    <t>Jaqson Tejada</t>
+  </si>
+  <si>
+    <t>Jacob Young</t>
+  </si>
+  <si>
+    <t>Drew Phillips</t>
+  </si>
+  <si>
+    <t>Kaden Frommelt</t>
+  </si>
+  <si>
+    <t>Manny Esparza</t>
+  </si>
+  <si>
+    <t>Luke Kehrli</t>
+  </si>
+  <si>
+    <t>Eli Green</t>
+  </si>
+  <si>
+    <t>Tyler Welch</t>
+  </si>
+  <si>
+    <t>Rylen Blair</t>
+  </si>
+  <si>
+    <t>Jalen Martinez</t>
+  </si>
+  <si>
+    <t>Nick Meyer</t>
+  </si>
+  <si>
+    <t>Parkland (NJCAA)</t>
+  </si>
+  <si>
+    <t>Gateway CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>Washington State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Creighton (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Jaylen Ziegler</t>
+  </si>
+  <si>
+    <t>Des Moines Area CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>Arizona (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Stats from 2024, At Iowa in 2025, did not play</t>
+  </si>
+  <si>
+    <t>Mount Mercy (NAIA)</t>
+  </si>
+  <si>
+    <t>Taft (CCCAA)</t>
+  </si>
+  <si>
+    <t>Webber Intl (NAIA)</t>
+  </si>
+  <si>
+    <t>Lewis (NCAA D2)</t>
+  </si>
+  <si>
+    <t>SP 6/8, 64</t>
+  </si>
+  <si>
+    <t>RP 6/8, 28</t>
+  </si>
+  <si>
+    <t>CP 6/7, 24</t>
+  </si>
+  <si>
+    <t>Black Hawk (NJCAA)</t>
+  </si>
+  <si>
+    <t>SP 6/3, 79</t>
+  </si>
+  <si>
+    <t>Sauk Valley (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 5/30, 30</t>
+  </si>
+  <si>
+    <t>Mount Marty (NAIA)</t>
+  </si>
+  <si>
+    <t>RP 5/28, 42</t>
+  </si>
+  <si>
+    <t>Butler CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/5, 34</t>
+  </si>
+  <si>
+    <t>Harper (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/8, 25</t>
+  </si>
+  <si>
+    <t>LSU Shreveport (NAIA)</t>
+  </si>
+  <si>
+    <t>RP 6/8, 22</t>
+  </si>
+  <si>
+    <t>Valparaiso (NCAA D1)</t>
+  </si>
+  <si>
+    <t>SP 6/6, 44</t>
+  </si>
+  <si>
+    <t>Grand Canyon (NCAA D1)</t>
+  </si>
+  <si>
+    <t>SP 6/7, 89</t>
+  </si>
+  <si>
+    <t>Lake County (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/6, 67</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Missouri Valley (NAIA)</t>
+  </si>
+  <si>
+    <t>SP 6/5, 54</t>
+  </si>
+  <si>
+    <t>Saint Leo (NCAA D2)</t>
+  </si>
+  <si>
+    <t>CP 6/6, 23</t>
+  </si>
+  <si>
+    <t>RP 6/5, 24</t>
+  </si>
+  <si>
+    <t>Walters State CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/7, 28</t>
+  </si>
+  <si>
+    <t>Whitworth (NCAA D3)</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1282,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode=".000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1036,8 +1305,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1068,6 +1343,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1082,7 +1363,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1145,9 +1426,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1168,19 +1446,103 @@
     <xf numFmtId="1" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="154">
+  <dxfs count="182">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1191,6 +1553,109 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1219,11 +1684,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode=".000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1255,66 +1748,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1892,23 +2325,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="181" dataDxfId="180">
   <autoFilter ref="A1:O19" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="151"/>
+    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="179"/>
     <tableColumn id="2" xr3:uid="{4B207364-C81F-4AB0-A7A1-6179ED226E0C}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="150"/>
-    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="148"/>
-    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="147"/>
-    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="146"/>
-    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="145"/>
-    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="144"/>
-    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="143"/>
-    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="142"/>
-    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="141"/>
-    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="140"/>
-    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="139"/>
+    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="178"/>
+    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="177"/>
+    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="176"/>
+    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="175"/>
+    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="174"/>
+    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="173"/>
+    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="172"/>
+    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="171"/>
+    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="170"/>
+    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="169"/>
+    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="168"/>
+    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="167"/>
     <tableColumn id="15" xr3:uid="{6F146679-03A5-4608-8323-E75FAFF903E6}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1916,45 +2349,45 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0843ECD0-6996-45AC-A9A9-494D040880A6}" name="Table2671011" displayName="Table2671011" ref="A1:L20" totalsRowShown="0" headerRowDxfId="6" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0843ECD0-6996-45AC-A9A9-494D040880A6}" name="Table2671011" displayName="Table2671011" ref="A1:L20" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:L20" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DDD953FD-5011-49C3-9230-44FD2E664EE4}" name="#" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{DDD953FD-5011-49C3-9230-44FD2E664EE4}" name="#" dataDxfId="52"/>
     <tableColumn id="2" xr3:uid="{C5B71AC5-1440-4ADE-BA98-FB907CC5B174}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{CE3006DC-DE43-451A-BE91-7DA1A81785E0}" name="Throws" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{B5E7AA9B-A56D-4805-BB36-39D375AE9533}" name="School" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{E42FD4B5-177E-4DFE-A2F5-247966E47C02}" name="ERA" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{33B5FF3A-1C37-4003-B2C4-C7CA9DF6D068}" name="IP" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{16EB2C0E-C141-4947-83DF-FAD21AE3D884}" name="H" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{998831EB-F6EF-4D4E-ACED-441C6839236E}" name="ER" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{56149B59-21AA-43DC-A628-D4B816C4BD8D}" name="HR" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{172AC206-5FBE-4E78-B1E1-C9DA83788B1B}" name="BB" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{E8C6BF8F-17A6-4CA1-B5EE-4010D8E6E237}" name="SO" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{411967A6-2B93-4978-A8B5-D67AEDB498DB}" name="Last PL Outing, NP" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{CE3006DC-DE43-451A-BE91-7DA1A81785E0}" name="Throws" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{B5E7AA9B-A56D-4805-BB36-39D375AE9533}" name="School" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{E42FD4B5-177E-4DFE-A2F5-247966E47C02}" name="ERA" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{33B5FF3A-1C37-4003-B2C4-C7CA9DF6D068}" name="IP" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{16EB2C0E-C141-4947-83DF-FAD21AE3D884}" name="H" dataDxfId="47"/>
+    <tableColumn id="10" xr3:uid="{998831EB-F6EF-4D4E-ACED-441C6839236E}" name="ER" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{56149B59-21AA-43DC-A628-D4B816C4BD8D}" name="HR" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{172AC206-5FBE-4E78-B1E1-C9DA83788B1B}" name="BB" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{E8C6BF8F-17A6-4CA1-B5EE-4010D8E6E237}" name="SO" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{411967A6-2B93-4978-A8B5-D67AEDB498DB}" name="Last PL Outing, NP" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{20B053F4-F88D-4429-AA41-68D802CD1DF8}" name="Table1458912" displayName="Table1458912" ref="A1:M19" totalsRowShown="0" headerRowDxfId="3" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{20B053F4-F88D-4429-AA41-68D802CD1DF8}" name="Table1458912" displayName="Table1458912" ref="A1:M19" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:M19" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{41FBD773-60D6-4C44-A4FB-F9B3AC2FF215}" name="#" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{41FBD773-60D6-4C44-A4FB-F9B3AC2FF215}" name="#" dataDxfId="39"/>
     <tableColumn id="2" xr3:uid="{7283EBB3-ECFD-4150-B86E-E64B8998B944}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{754D84E1-E5E5-4628-BE76-6FC3F40A499D}" name="School" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{831F66A7-878D-4156-94CB-7A6FAC523764}" name="PA" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{3415C3C4-46AA-480E-9A6C-26B96A96F229}" name="H" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{79AF8C5A-6B40-47EB-AE42-4B6470FC7335}" name="HR" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{7199D5C9-AF2B-4B9A-B085-659C519522A1}" name="BB" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{951AAA57-6EF3-4291-812C-F7231AB5B201}" name="SO" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{C58BF7E3-497D-4DA5-A7AD-A0DA6D6F35FE}" name="AVG" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{E7A8FCAD-07A0-4F17-BD83-CD5B529C19EF}" name="OBP" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{6CC324F1-66DA-48AB-8C9A-BDD8D93CC895}" name="SB" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{DE70BA46-0B42-4F84-BC0E-499D6EF099B4}" name="K%" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{754D84E1-E5E5-4628-BE76-6FC3F40A499D}" name="School" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{831F66A7-878D-4156-94CB-7A6FAC523764}" name="PA" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{3415C3C4-46AA-480E-9A6C-26B96A96F229}" name="H" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{79AF8C5A-6B40-47EB-AE42-4B6470FC7335}" name="HR" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{7199D5C9-AF2B-4B9A-B085-659C519522A1}" name="BB" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{951AAA57-6EF3-4291-812C-F7231AB5B201}" name="SO" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{C58BF7E3-497D-4DA5-A7AD-A0DA6D6F35FE}" name="AVG" dataDxfId="32"/>
+    <tableColumn id="17" xr3:uid="{E7A8FCAD-07A0-4F17-BD83-CD5B529C19EF}" name="OBP" dataDxfId="31"/>
+    <tableColumn id="19" xr3:uid="{6CC324F1-66DA-48AB-8C9A-BDD8D93CC895}" name="SB" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{DE70BA46-0B42-4F84-BC0E-499D6EF099B4}" name="K%" dataDxfId="29">
       <calculatedColumnFormula>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6D28691B-C12C-444A-8445-978CAEDE2F9E}" name="BB%" dataDxfId="0" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{6D28691B-C12C-444A-8445-978CAEDE2F9E}" name="BB%" dataDxfId="28" dataCellStyle="Percent">
       <calculatedColumnFormula>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1962,29 +2395,77 @@
 </table>
 </file>
 
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1E8C808E-02A8-46BA-AA9E-A0D655CEA28C}" name="Table267101113" displayName="Table267101113" ref="A1:L22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="27">
+  <autoFilter ref="A1:L22" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{53D3A89E-97BA-4F08-B0AD-FEE71660E94D}" name="#" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{4F0D2D19-1FA0-4730-BACA-A68D1EAF3453}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{FFBBB80F-B1A8-4EC8-976C-085201346C4D}" name="Throws" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{DE2D8D5C-2C62-455D-B77C-056B3E753E69}" name="School" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{9B3DC61A-0F76-44C1-BF9D-18954F72727A}" name="ERA" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{6D73B12E-18A1-45CA-9B08-9C1F49C331A4}" name="IP" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{ED2C7A8D-0CC4-48B4-AFAD-76907FFF619F}" name="H" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{4847CBFF-7F85-4920-B0CA-AFA3CA5E9647}" name="ER" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{7A4AE25A-68AB-4E07-89DC-44175FE1658D}" name="HR" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{C3ABA9DC-4AE3-4DB8-938A-74AF7FC956A7}" name="BB" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{92CDCC4A-9682-4E76-9232-2F4E4221A30C}" name="SO" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{D07BD69A-6BC8-4751-BDE9-1EEE5F758A61}" name="Last PL Outing, NP" dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C4498885-CE91-45F0-BBCE-FA920BC3B339}" name="Table145891214" displayName="Table145891214" ref="A1:N25" totalsRowShown="0" headerRowDxfId="1" dataDxfId="18">
+  <autoFilter ref="A1:N25" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{16B85A6F-BC64-43BE-A54D-1F0B342237E0}" name="#" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{BECFA166-D20C-4030-BDA2-6CBE958455B1}" name="Name"/>
+    <tableColumn id="5" xr3:uid="{B350053F-F69C-4349-AF75-A1C7D5CD441D}" name="School" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{CF009ACA-9A74-4B56-862C-F9D66C2AF6ED}" name="PA" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{B77625E8-C799-452D-BD3B-F54240A37442}" name="H" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{25DA73CE-B909-4BC6-87D2-63A7D47C7794}" name="HR" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{EB22A26E-B003-438D-946C-E282A958EB33}" name="BB" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{4EBAAB28-9C02-46B5-B028-4C01FD67FBF1}" name="SO" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{51CB3843-53F2-4E57-808F-E8A84FC824BC}" name="AVG" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{0BDDFC3E-0828-4A0F-9C42-6F5E0E5B37E8}" name="OBP" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{1ED150C3-4B5D-49FA-94CA-65AA661B2BDA}" name="SB" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{5140C3F1-FD3F-4557-9157-73F8F239BD1C}" name="K%" dataDxfId="7">
+      <calculatedColumnFormula>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{8BAE2FE2-C84A-4386-AA69-C3A582E43681}" name="BB%" dataDxfId="6" dataCellStyle="Percent">
+      <calculatedColumnFormula>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{AB87AD4A-D692-4DED-9C8F-8D6B85C3CE7E}" name="Notes" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="138" dataDxfId="137">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="166" dataDxfId="165">
   <autoFilter ref="A1:T20" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="136"/>
+    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="164"/>
     <tableColumn id="2" xr3:uid="{1E71FAB3-5F80-433A-9CF9-976B18697772}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="135"/>
-    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="134"/>
-    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="133"/>
-    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="132"/>
-    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="131"/>
-    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="130"/>
-    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="129"/>
-    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="128"/>
-    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="127"/>
-    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="126"/>
-    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="125"/>
-    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="124"/>
-    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="123"/>
-    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="122"/>
-    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="121"/>
-    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="120"/>
-    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="163"/>
+    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="162"/>
+    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="161"/>
+    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="160"/>
+    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="159"/>
+    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="158"/>
+    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="157"/>
+    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="156"/>
+    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="155"/>
+    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="154"/>
+    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="153"/>
+    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="152"/>
+    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="151"/>
+    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="150"/>
+    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="149"/>
+    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="148"/>
+    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="147"/>
     <tableColumn id="20" xr3:uid="{63D55BB7-68A9-437C-9C45-35CEA0F3FE2B}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1992,26 +2473,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="146" dataDxfId="145">
   <autoFilter ref="A32:R51" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="116"/>
+    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="144"/>
     <tableColumn id="2" xr3:uid="{ABA958D3-F28A-4755-9648-E1D80184B0D4}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="115"/>
-    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="114"/>
-    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="113"/>
-    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="112"/>
-    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="111"/>
-    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="110"/>
-    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="109"/>
-    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="108"/>
-    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="107"/>
-    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="106"/>
-    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="105"/>
-    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="104"/>
-    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="103"/>
-    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="102"/>
-    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="101"/>
+    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="143"/>
+    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="142"/>
+    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="141"/>
+    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="140"/>
+    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="139"/>
+    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="138"/>
+    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="137"/>
+    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="136"/>
+    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="135"/>
+    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="134"/>
+    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="133"/>
+    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="132"/>
+    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="131"/>
+    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="130"/>
+    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="129"/>
     <tableColumn id="20" xr3:uid="{D6FD6B3E-0891-49E1-9B8B-AEF67C143114}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2019,20 +2500,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="100" dataDxfId="99">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="128" dataDxfId="127">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="126"/>
     <tableColumn id="2" xr3:uid="{516EEF33-51BA-4936-98F6-F4E8C86D9AB9}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="93"/>
-    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="92"/>
-    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="91"/>
-    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="90"/>
-    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="125"/>
+    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="124"/>
+    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="123"/>
+    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="122"/>
+    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="121"/>
+    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="118"/>
+    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="117"/>
     <tableColumn id="15" xr3:uid="{2568029A-6AFC-43E6-B446-46528B9915F4}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2040,20 +2521,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115">
   <autoFilter ref="A1:L20" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="114"/>
     <tableColumn id="2" xr3:uid="{984187B9-FA1E-4DBC-B804-6E035D1B61A2}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="84"/>
-    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="83"/>
-    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="82"/>
-    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="81"/>
-    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="80"/>
-    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="79"/>
-    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="78"/>
-    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="110"/>
+    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="109"/>
+    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="108"/>
+    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="107"/>
+    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="106"/>
+    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="105"/>
     <tableColumn id="20" xr3:uid="{9348918D-5ECB-448B-A085-487540424189}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2061,82 +2542,82 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103">
   <autoFilter ref="A1:K19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="102"/>
     <tableColumn id="2" xr3:uid="{FD907DA6-0C2B-490D-862C-004A3C98FA20}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="68"/>
-    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="67"/>
-    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="66"/>
-    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="101"/>
+    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="100"/>
+    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="99"/>
+    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="97"/>
+    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="95"/>
+    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="94"/>
+    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
   <autoFilter ref="A1:K17" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="62"/>
+    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="90"/>
     <tableColumn id="2" xr3:uid="{A108195E-3469-4ACD-AA5B-AAB9CB14C59B}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="59"/>
-    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="57"/>
-    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="56"/>
-    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="55"/>
-    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="54"/>
-    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="89"/>
+    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="87"/>
+    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="86"/>
+    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="85"/>
+    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="84"/>
+    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="83"/>
+    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="82"/>
+    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="50"/>
+    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="78"/>
     <tableColumn id="2" xr3:uid="{6377AB1F-C5EE-4699-A482-9F1094364D72}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
   <autoFilter ref="A1:L15" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="65"/>
     <tableColumn id="2" xr3:uid="{F0F04FB6-1130-4097-843F-75D32B7FDEAA}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="36"/>
-    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="34"/>
-    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="31"/>
-    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="29"/>
-    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="61"/>
+    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="60"/>
+    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="59"/>
+    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="58"/>
+    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="57"/>
+    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3236,48 +3717,48 @@
     <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="30"/>
+    <col min="9" max="10" width="9.140625" style="29"/>
     <col min="12" max="12" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="24" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3306,20 +3787,20 @@
       <c r="H2" s="1">
         <v>29</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <v>0.311</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="27">
         <v>0.41499999999999998</v>
       </c>
       <c r="K2" s="6">
         <v>14</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.15183246073298429</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.12041884816753927</v>
       </c>
@@ -3349,20 +3830,20 @@
       <c r="H3" s="11">
         <v>13</v>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="28">
         <v>0.20799999999999999</v>
       </c>
-      <c r="J3" s="29">
+      <c r="J3" s="28">
         <v>0.247</v>
       </c>
       <c r="K3" s="11">
         <v>1</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.15853658536585366</v>
       </c>
-      <c r="M3" s="35">
+      <c r="M3" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>4.878048780487805E-2</v>
       </c>
@@ -3392,20 +3873,20 @@
       <c r="H4" s="11">
         <v>8</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="28">
         <v>0.29699999999999999</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="28">
         <v>0.40899999999999997</v>
       </c>
       <c r="K4" s="11">
         <v>3</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.13636363636363635</v>
       </c>
@@ -3438,20 +3919,20 @@
       <c r="H5" s="1">
         <v>15</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="27">
         <v>0.121</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="27">
         <v>0.17100000000000001</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="M5" s="35">
+      <c r="M5" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>5.7142857142857141E-2</v>
       </c>
@@ -3484,20 +3965,20 @@
       <c r="H6" s="11">
         <v>28</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="28">
         <v>0.218</v>
       </c>
-      <c r="J6" s="29">
+      <c r="J6" s="28">
         <v>0.34300000000000003</v>
       </c>
       <c r="K6" s="11">
         <v>6</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.16</v>
       </c>
-      <c r="M6" s="35">
+      <c r="M6" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.14285714285714285</v>
       </c>
@@ -3527,20 +4008,20 @@
       <c r="H7" s="1">
         <v>38</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <v>0.22800000000000001</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="27">
         <v>0.38800000000000001</v>
       </c>
       <c r="K7" s="6">
         <v>10</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.25675675675675674</v>
       </c>
-      <c r="M7" s="35">
+      <c r="M7" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.1554054054054054</v>
       </c>
@@ -3570,20 +4051,20 @@
       <c r="H8" s="1">
         <v>6</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="27">
         <v>0.2</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>7.1428571428571425E-2</v>
       </c>
@@ -3613,20 +4094,20 @@
       <c r="H9" s="1">
         <v>38</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <v>0.221</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="27">
         <v>0.36899999999999999</v>
       </c>
       <c r="K9" s="6">
         <v>2</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.27142857142857141</v>
       </c>
-      <c r="M9" s="35">
+      <c r="M9" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.12142857142857143</v>
       </c>
@@ -3656,20 +4137,20 @@
       <c r="H10" s="1">
         <v>12</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <v>0.36399999999999999</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="27">
         <v>0.46700000000000003</v>
       </c>
       <c r="K10" s="6">
         <v>7</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>8.7591240875912413E-2</v>
       </c>
-      <c r="M10" s="35">
+      <c r="M10" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.13868613138686131</v>
       </c>
@@ -3699,20 +4180,20 @@
       <c r="H11" s="1">
         <v>20</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="28">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="28">
         <v>0.36899999999999999</v>
       </c>
       <c r="K11" s="6">
         <v>1</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.23255813953488372</v>
       </c>
-      <c r="M11" s="35">
+      <c r="M11" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>9.3023255813953487E-2</v>
       </c>
@@ -3742,20 +4223,20 @@
       <c r="H12" s="1">
         <v>19</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="27">
         <v>0.11799999999999999</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="27">
         <v>0.189</v>
       </c>
       <c r="K12" s="6">
         <v>0</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.51351351351351349</v>
       </c>
-      <c r="M12" s="35">
+      <c r="M12" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>8.1081081081081086E-2</v>
       </c>
@@ -3785,20 +4266,20 @@
       <c r="H13" s="11">
         <v>15</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="28">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J13" s="29">
+      <c r="J13" s="28">
         <v>0.53100000000000003</v>
       </c>
       <c r="K13" s="11">
         <v>39</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="M13" s="35">
+      <c r="M13" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.13333333333333333</v>
       </c>
@@ -3828,20 +4309,20 @@
       <c r="H14" s="1">
         <v>23</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="27">
         <v>0.30499999999999999</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="27">
         <v>0.40400000000000003</v>
       </c>
       <c r="K14" s="6">
         <v>15</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.12234042553191489</v>
       </c>
-      <c r="M14" s="35">
+      <c r="M14" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.1276595744680851</v>
       </c>
@@ -3871,20 +4352,20 @@
       <c r="H15" s="1">
         <v>11</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="27">
         <v>0.33900000000000002</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="27">
         <v>0.39700000000000002</v>
       </c>
       <c r="K15" s="6">
         <v>0</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="M15" s="35">
+      <c r="M15" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>6.6115702479338845E-2</v>
       </c>
@@ -3914,20 +4395,20 @@
       <c r="H16" s="1">
         <v>20</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="27">
         <v>0.121</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="27">
         <v>0.19400000000000001</v>
       </c>
       <c r="K16" s="6">
         <v>0</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.55555555555555558</v>
       </c>
-      <c r="M16" s="35">
+      <c r="M16" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -3960,20 +4441,20 @@
       <c r="H17" s="1">
         <v>23</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="27">
         <v>0.34</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="27">
         <v>0.45200000000000001</v>
       </c>
       <c r="K17" s="6">
         <v>10</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>9.5435684647302899E-2</v>
       </c>
-      <c r="M17" s="35">
+      <c r="M17" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.13278008298755187</v>
       </c>
@@ -4003,20 +4484,20 @@
       <c r="H18" s="1">
         <v>27</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="27">
         <v>0.29399999999999998</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="27">
         <v>0.42</v>
       </c>
       <c r="K18" s="6">
         <v>14</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.11739130434782609</v>
       </c>
-      <c r="M18" s="35">
+      <c r="M18" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.15217391304347827</v>
       </c>
@@ -4046,23 +4527,2033 @@
       <c r="H19" s="1">
         <v>8</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="27">
         <v>0.19</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="27">
         <v>0.32</v>
       </c>
       <c r="K19" s="6">
         <v>1</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="32">
         <f>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.27586206896551724</v>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="33">
         <f>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</f>
         <v>0.13793103448275862</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF32274F-97FD-44A9-AABD-4A9ED509BDB2}">
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="E2" s="35">
+        <v>13.5</v>
+      </c>
+      <c r="F2" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6</v>
+      </c>
+      <c r="H2" s="11">
+        <v>5</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>7</v>
+      </c>
+      <c r="K2" s="11">
+        <v>4</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="35">
+        <v>7.12</v>
+      </c>
+      <c r="F3" s="11">
+        <v>30.1</v>
+      </c>
+      <c r="G3" s="11">
+        <v>39</v>
+      </c>
+      <c r="H3" s="11">
+        <v>24</v>
+      </c>
+      <c r="I3" s="11">
+        <v>4</v>
+      </c>
+      <c r="J3" s="11">
+        <v>3</v>
+      </c>
+      <c r="K3" s="11">
+        <v>30</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="P3" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q3" s="23">
+        <v>45807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E4" s="5">
+        <v>7.71</v>
+      </c>
+      <c r="F4" s="1">
+        <v>30.1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>47</v>
+      </c>
+      <c r="H4" s="1">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>21</v>
+      </c>
+      <c r="K4" s="1">
+        <v>18</v>
+      </c>
+      <c r="L4" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="P4" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>45808</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6.23</v>
+      </c>
+      <c r="F5" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>3</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>381</v>
+      </c>
+      <c r="P5" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3.15</v>
+      </c>
+      <c r="F6" s="16">
+        <v>60</v>
+      </c>
+      <c r="G6" s="1">
+        <v>48</v>
+      </c>
+      <c r="H6" s="1">
+        <v>21</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>25</v>
+      </c>
+      <c r="K6" s="1">
+        <v>83</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="P6" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>45811</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="5">
+        <v>8.1</v>
+      </c>
+      <c r="F7" s="16">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1">
+        <v>18</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>15</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="P7" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>45812</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E8" s="5">
+        <v>6.51</v>
+      </c>
+      <c r="F8" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1">
+        <v>25</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="P8" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>45813</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="E9" s="5">
+        <v>37.130000000000003</v>
+      </c>
+      <c r="F9" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G9" s="1">
+        <v>7</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>4</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q9" s="23"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10" s="35">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="F10" s="17">
+        <v>49.2</v>
+      </c>
+      <c r="G10" s="11">
+        <v>29</v>
+      </c>
+      <c r="H10" s="11">
+        <v>24</v>
+      </c>
+      <c r="I10" s="11">
+        <v>6</v>
+      </c>
+      <c r="J10" s="11">
+        <v>12</v>
+      </c>
+      <c r="K10" s="11">
+        <v>38</v>
+      </c>
+      <c r="L10" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q10" s="23"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" s="5">
+        <v>3.21</v>
+      </c>
+      <c r="F11" s="16">
+        <v>47.2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>40</v>
+      </c>
+      <c r="H11" s="1">
+        <v>17</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>24</v>
+      </c>
+      <c r="K11" s="1">
+        <v>54</v>
+      </c>
+      <c r="L11" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q11" s="23"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3.18</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6</v>
+      </c>
+      <c r="K12" s="1">
+        <v>7</v>
+      </c>
+      <c r="L12" s="34" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" s="5">
+        <v>7.62</v>
+      </c>
+      <c r="F13" s="16">
+        <v>26</v>
+      </c>
+      <c r="G13" s="1">
+        <v>34</v>
+      </c>
+      <c r="H13" s="1">
+        <v>22</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
+      </c>
+      <c r="J13" s="1">
+        <v>17</v>
+      </c>
+      <c r="K13" s="1">
+        <v>23</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7.76</v>
+      </c>
+      <c r="F14" s="16">
+        <v>51</v>
+      </c>
+      <c r="G14" s="1">
+        <v>67</v>
+      </c>
+      <c r="H14" s="1">
+        <v>44</v>
+      </c>
+      <c r="I14" s="6">
+        <v>7</v>
+      </c>
+      <c r="J14" s="6">
+        <v>32</v>
+      </c>
+      <c r="K14" s="6">
+        <v>31</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7.33</v>
+      </c>
+      <c r="F15" s="16">
+        <v>27</v>
+      </c>
+      <c r="G15" s="1">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1">
+        <v>22</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>18</v>
+      </c>
+      <c r="K15" s="1">
+        <v>29</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>355</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E16" s="35">
+        <v>5.67</v>
+      </c>
+      <c r="F16" s="17">
+        <v>54</v>
+      </c>
+      <c r="G16" s="11">
+        <v>55</v>
+      </c>
+      <c r="H16" s="11">
+        <v>34</v>
+      </c>
+      <c r="I16" s="11">
+        <v>7</v>
+      </c>
+      <c r="J16" s="11">
+        <v>16</v>
+      </c>
+      <c r="K16" s="11">
+        <v>50</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4.25</v>
+      </c>
+      <c r="F17" s="16">
+        <v>53</v>
+      </c>
+      <c r="G17" s="1">
+        <v>41</v>
+      </c>
+      <c r="H17" s="1">
+        <v>25</v>
+      </c>
+      <c r="I17" s="1">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1">
+        <v>29</v>
+      </c>
+      <c r="K17" s="1">
+        <v>53</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E18" s="5">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="F18" s="16">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3</v>
+      </c>
+      <c r="K18" s="1">
+        <v>4</v>
+      </c>
+      <c r="L18" s="34" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>361</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E19" s="5">
+        <v>9.26</v>
+      </c>
+      <c r="F19" s="16">
+        <v>11.2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>12</v>
+      </c>
+      <c r="H19" s="1">
+        <v>12</v>
+      </c>
+      <c r="I19" s="1">
+        <v>3</v>
+      </c>
+      <c r="J19" s="1">
+        <v>9</v>
+      </c>
+      <c r="K19" s="1">
+        <v>7</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>362</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="F20" s="16">
+        <v>18</v>
+      </c>
+      <c r="G20" s="1">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>15</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4.42</v>
+      </c>
+      <c r="F21" s="1">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="G21" s="1">
+        <v>33</v>
+      </c>
+      <c r="H21" s="1">
+        <v>18</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2</v>
+      </c>
+      <c r="J21" s="1">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1">
+        <v>40</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E22" s="5">
+        <v>6.75</v>
+      </c>
+      <c r="F22" s="16">
+        <v>20</v>
+      </c>
+      <c r="G22" s="1">
+        <v>22</v>
+      </c>
+      <c r="H22" s="1">
+        <v>15</v>
+      </c>
+      <c r="I22" s="1">
+        <v>2</v>
+      </c>
+      <c r="J22" s="1">
+        <v>9</v>
+      </c>
+      <c r="K22" s="1">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EA80240-98D5-48DF-A329-D03EF476277E}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" style="29"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="14" max="14" width="42.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="N1" s="36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="1">
+        <v>93</v>
+      </c>
+      <c r="E2" s="1">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1">
+        <v>27</v>
+      </c>
+      <c r="I2" s="27">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="J2" s="27">
+        <v>0.315</v>
+      </c>
+      <c r="K2" s="6">
+        <v>27</v>
+      </c>
+      <c r="L2" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.29032258064516131</v>
+      </c>
+      <c r="M2" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>7.5268817204301078E-2</v>
+      </c>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="11">
+        <v>223</v>
+      </c>
+      <c r="E3" s="11">
+        <v>76</v>
+      </c>
+      <c r="F3" s="11">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11">
+        <v>33</v>
+      </c>
+      <c r="H3" s="11">
+        <v>23</v>
+      </c>
+      <c r="I3" s="28">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="J3" s="28">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="K3" s="11">
+        <v>9</v>
+      </c>
+      <c r="L3" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.1031390134529148</v>
+      </c>
+      <c r="M3" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.14798206278026907</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="1">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9</v>
+      </c>
+      <c r="I5" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="27">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="M5" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="11">
+        <v>143</v>
+      </c>
+      <c r="E6" s="11">
+        <v>39</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1</v>
+      </c>
+      <c r="G6" s="11">
+        <v>24</v>
+      </c>
+      <c r="H6" s="11">
+        <v>19</v>
+      </c>
+      <c r="I6" s="28">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="J6" s="28">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="K6" s="11">
+        <v>8</v>
+      </c>
+      <c r="L6" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.13286713286713286</v>
+      </c>
+      <c r="M6" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.16783216783216784</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D7" s="1">
+        <v>170</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>54</v>
+      </c>
+      <c r="I7" s="27">
+        <v>0.224</v>
+      </c>
+      <c r="J7" s="27">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="K7" s="6">
+        <v>15</v>
+      </c>
+      <c r="L7" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.31764705882352939</v>
+      </c>
+      <c r="M7" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.12941176470588237</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="1">
+        <v>59</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>8</v>
+      </c>
+      <c r="H8" s="1">
+        <v>19</v>
+      </c>
+      <c r="I8" s="27">
+        <v>0.114</v>
+      </c>
+      <c r="J8" s="27">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.32203389830508472</v>
+      </c>
+      <c r="M8" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.13559322033898305</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="1">
+        <v>93</v>
+      </c>
+      <c r="E10" s="1">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1">
+        <v>23</v>
+      </c>
+      <c r="I10" s="27">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="J10" s="27">
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="K10" s="6">
+        <v>5</v>
+      </c>
+      <c r="L10" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.24731182795698925</v>
+      </c>
+      <c r="M10" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.10752688172043011</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="1">
+        <v>98</v>
+      </c>
+      <c r="E11" s="1">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="28">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="J11" s="28">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K11" s="6">
+        <v>3</v>
+      </c>
+      <c r="L11" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="M11" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>9.1836734693877556E-2</v>
+      </c>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" s="11">
+        <v>286</v>
+      </c>
+      <c r="E13" s="11">
+        <v>57</v>
+      </c>
+      <c r="F13" s="11">
+        <v>5</v>
+      </c>
+      <c r="G13" s="11">
+        <v>24</v>
+      </c>
+      <c r="H13" s="11">
+        <v>68</v>
+      </c>
+      <c r="I13" s="28">
+        <v>0.246</v>
+      </c>
+      <c r="J13" s="28">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="K13" s="11">
+        <v>44</v>
+      </c>
+      <c r="L13" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.23776223776223776</v>
+      </c>
+      <c r="M13" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>8.3916083916083919E-2</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46</v>
+      </c>
+      <c r="E15" s="1">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1">
+        <v>9</v>
+      </c>
+      <c r="I15" s="27">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="J15" s="27">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.19565217391304349</v>
+      </c>
+      <c r="M15" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>6.5217391304347824E-2</v>
+      </c>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>346</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D16" s="1">
+        <v>165</v>
+      </c>
+      <c r="E16" s="1">
+        <v>43</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1">
+        <v>31</v>
+      </c>
+      <c r="I16" s="27">
+        <v>0.307</v>
+      </c>
+      <c r="J16" s="27">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="K16" s="6">
+        <v>8</v>
+      </c>
+      <c r="L16" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.18787878787878787</v>
+      </c>
+      <c r="M16" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="1">
+        <v>6</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="J18" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M18" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>352</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D19" s="1">
+        <v>175</v>
+      </c>
+      <c r="E19" s="1">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>20</v>
+      </c>
+      <c r="H19" s="1">
+        <v>26</v>
+      </c>
+      <c r="I19" s="27">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="J19" s="27">
+        <v>0.44</v>
+      </c>
+      <c r="K19" s="6">
+        <v>10</v>
+      </c>
+      <c r="L19" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.14857142857142858</v>
+      </c>
+      <c r="M19" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>35</v>
+      </c>
+      <c r="B20" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D20" s="1">
+        <v>154</v>
+      </c>
+      <c r="E20" s="1">
+        <v>45</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>15</v>
+      </c>
+      <c r="H20" s="1">
+        <v>30</v>
+      </c>
+      <c r="I20" s="27">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="J20" s="27">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="K20" s="6">
+        <v>6</v>
+      </c>
+      <c r="L20" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.19480519480519481</v>
+      </c>
+      <c r="M20" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>9.7402597402597407E-2</v>
+      </c>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" s="1">
+        <v>30</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1">
+        <v>13</v>
+      </c>
+      <c r="I21" s="27">
+        <v>0.115</v>
+      </c>
+      <c r="J21" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="K21" s="6">
+        <v>0</v>
+      </c>
+      <c r="L21" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="M21" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>359</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" s="1">
+        <v>185</v>
+      </c>
+      <c r="E22" s="1">
+        <v>45</v>
+      </c>
+      <c r="F22" s="1">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="27">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="J22" s="27">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="K22" s="6">
+        <v>4</v>
+      </c>
+      <c r="L22" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="M22" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>8.1081081081081086E-2</v>
+      </c>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>360</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="D23" s="1">
+        <v>116</v>
+      </c>
+      <c r="E23" s="1">
+        <v>13</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>14</v>
+      </c>
+      <c r="H23" s="1">
+        <v>28</v>
+      </c>
+      <c r="I23" s="27">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="J23" s="27">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0</v>
+      </c>
+      <c r="L23" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="M23" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>93</v>
+      </c>
+      <c r="B24" t="s">
+        <v>365</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="D24" s="1">
+        <v>213</v>
+      </c>
+      <c r="E24" s="1">
+        <v>59</v>
+      </c>
+      <c r="F24" s="1">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1">
+        <v>22</v>
+      </c>
+      <c r="H24" s="1">
+        <v>28</v>
+      </c>
+      <c r="I24" s="27">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="J24" s="27">
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="K24" s="6">
+        <v>5</v>
+      </c>
+      <c r="L24" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.13145539906103287</v>
+      </c>
+      <c r="M24" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.10328638497652583</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D25" s="1">
+        <v>128</v>
+      </c>
+      <c r="E25" s="1">
+        <v>25</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1">
+        <v>15</v>
+      </c>
+      <c r="H25" s="1">
+        <v>22</v>
+      </c>
+      <c r="I25" s="27">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="J25" s="27">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="K25" s="6">
+        <v>0</v>
+      </c>
+      <c r="L25" s="32">
+        <f>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.171875</v>
+      </c>
+      <c r="M25" s="33">
+        <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
+        <v>0.1171875</v>
+      </c>
+      <c r="N25" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10222,40 +12713,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>197</v>
       </c>
     </row>
@@ -10595,7 +13086,7 @@
       <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="1" t="s">
         <v>285</v>
       </c>
       <c r="Q9" s="23"/>
@@ -10634,7 +13125,7 @@
       <c r="K10" s="11">
         <v>21</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="1" t="s">
         <v>289</v>
       </c>
       <c r="Q10" s="23"/>
@@ -10712,7 +13203,7 @@
       <c r="K12" s="1">
         <v>64</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="1" t="s">
         <v>296</v>
       </c>
     </row>

--- a/CornBelters/Scouting Reports/Tables.xlsx
+++ b/CornBelters/Scouting Reports/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Cornbelters\Kernelytics-Projects\CornBelters\Scouting Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03BEFDC-C9A0-4B99-BE0E-5B2095D5E403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E304A13-AF81-43BF-BD9D-89AE13982F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="5" activeTab="10" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="6" activeTab="12" xr2:uid="{4B97C0AA-4F54-4EC4-A9DB-CD535EEAB5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Pitchers (Spring Stats)" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="ChillicotheSpringHitting" sheetId="13" r:id="rId10"/>
     <sheet name="ClintonSpringPitching" sheetId="14" r:id="rId11"/>
     <sheet name="ClintonSpringHitting" sheetId="15" r:id="rId12"/>
+    <sheet name="JacksonSpringPitching" sheetId="18" r:id="rId13"/>
+    <sheet name="JacksonSpringHitting" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="500">
   <si>
     <t>#</t>
   </si>
@@ -1271,6 +1273,282 @@
   </si>
   <si>
     <t>Whitworth (NCAA D3)</t>
+  </si>
+  <si>
+    <t>Elijah Dunbar</t>
+  </si>
+  <si>
+    <t>Point (NAIA)</t>
+  </si>
+  <si>
+    <t>RP 6/10. 21</t>
+  </si>
+  <si>
+    <t>McKay Whitaker</t>
+  </si>
+  <si>
+    <t>Bellarmine (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Drew McConnell</t>
+  </si>
+  <si>
+    <t>Ivan Vega</t>
+  </si>
+  <si>
+    <t>Bethel (NAIA)</t>
+  </si>
+  <si>
+    <t>Lawson Ryan</t>
+  </si>
+  <si>
+    <t>Christian Brothers (NCAA D2)</t>
+  </si>
+  <si>
+    <t>SP 6/10, 83</t>
+  </si>
+  <si>
+    <t>Jack Mclaury</t>
+  </si>
+  <si>
+    <t>Volunteer State CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/6, 14</t>
+  </si>
+  <si>
+    <t>Jack Pitts</t>
+  </si>
+  <si>
+    <t>Memphis (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Drake Blackwood</t>
+  </si>
+  <si>
+    <t>Freed-Hardeman (NAIA)</t>
+  </si>
+  <si>
+    <t>Andrew Perry</t>
+  </si>
+  <si>
+    <t>SP 6/8, 82</t>
+  </si>
+  <si>
+    <t>Merrick Hill</t>
+  </si>
+  <si>
+    <t>Morton (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/6, 23</t>
+  </si>
+  <si>
+    <t>Parks Bouck</t>
+  </si>
+  <si>
+    <t>Lipscomb (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Hunter McLemore</t>
+  </si>
+  <si>
+    <t>RP 6/5, 59</t>
+  </si>
+  <si>
+    <t>Brett Rogers</t>
+  </si>
+  <si>
+    <t>Matthew Riley</t>
+  </si>
+  <si>
+    <t>Middle Tennessee (NCAA D1)</t>
+  </si>
+  <si>
+    <t>SP 6/12, 97</t>
+  </si>
+  <si>
+    <t>Jett Sutton</t>
+  </si>
+  <si>
+    <t>Arkansas State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>SP 5/30, 83</t>
+  </si>
+  <si>
+    <t>Mason Acton</t>
+  </si>
+  <si>
+    <t>Joe Romines</t>
+  </si>
+  <si>
+    <t>RP 6/12, 8</t>
+  </si>
+  <si>
+    <t>Brooks Jones</t>
+  </si>
+  <si>
+    <t>Jacob Rossi</t>
+  </si>
+  <si>
+    <t>RP 6/10, 26</t>
+  </si>
+  <si>
+    <t>Jaxson Lucas</t>
+  </si>
+  <si>
+    <t>CP 6/6, 14</t>
+  </si>
+  <si>
+    <t>Chase Chamberlain</t>
+  </si>
+  <si>
+    <t>SP 6/7, 76</t>
+  </si>
+  <si>
+    <t>Webb Watson</t>
+  </si>
+  <si>
+    <t>Trey Watson</t>
+  </si>
+  <si>
+    <t>Mobile (NAIA)</t>
+  </si>
+  <si>
+    <t>Bradey Moad</t>
+  </si>
+  <si>
+    <t>Olney Central CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>Cameron Greene</t>
+  </si>
+  <si>
+    <t>UT Martin (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Connor Busson</t>
+  </si>
+  <si>
+    <t>Gardner-Webb (NCAA D1)</t>
+  </si>
+  <si>
+    <t>RP 6/8, 78</t>
+  </si>
+  <si>
+    <t>Adriel Vega</t>
+  </si>
+  <si>
+    <t>Brody Casteel</t>
+  </si>
+  <si>
+    <t>Cleveland State CC (NJCAA)</t>
+  </si>
+  <si>
+    <t>RP 6/6, 21</t>
+  </si>
+  <si>
+    <t>Jack Runsick</t>
+  </si>
+  <si>
+    <t>Eastern Oklahoma (NJCAA)</t>
+  </si>
+  <si>
+    <t>Chase Armstrong</t>
+  </si>
+  <si>
+    <t>RP 6/4, 45</t>
+  </si>
+  <si>
+    <t>Cole Lannom</t>
+  </si>
+  <si>
+    <t>RP 6/8, 26</t>
+  </si>
+  <si>
+    <t>Cade Miles</t>
+  </si>
+  <si>
+    <t>Jacksonville State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Jackson Campbell</t>
+  </si>
+  <si>
+    <t>St. Joseph (NCAA D1)</t>
+  </si>
+  <si>
+    <t>RP 6/11, 18</t>
+  </si>
+  <si>
+    <t>Ethan Ell</t>
+  </si>
+  <si>
+    <t>Kentucky Wesleyan (NCAA D2)</t>
+  </si>
+  <si>
+    <t>RP 6/10, 44</t>
+  </si>
+  <si>
+    <t>Nathan Rhodes</t>
+  </si>
+  <si>
+    <t>RP 6/12, 9</t>
+  </si>
+  <si>
+    <t>Mason Clark</t>
+  </si>
+  <si>
+    <t>RP 6/12, 16</t>
+  </si>
+  <si>
+    <t>Charlie Jury</t>
+  </si>
+  <si>
+    <t>Murray State (NCAA D1)</t>
+  </si>
+  <si>
+    <t>Jake Maddox</t>
+  </si>
+  <si>
+    <t>Cooper Casteel</t>
+  </si>
+  <si>
+    <t>Lee University (NCAA D2)</t>
+  </si>
+  <si>
+    <t>SP 6/6, 82</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>Hill</t>
+  </si>
+  <si>
+    <t>Riley</t>
+  </si>
+  <si>
+    <t>Chamberlain</t>
+  </si>
+  <si>
+    <t>Sutton</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>Casteel</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>SP 6/11, 99</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1590,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1349,6 +1627,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1363,7 +1647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1452,9 +1736,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1474,12 +1755,218 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="182">
+  <dxfs count="211">
+    <dxf>
+      <numFmt numFmtId="21" formatCode="d\-mmm"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode=".000"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1506,6 +1993,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1531,90 +2055,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode=".000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode=".000"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2325,23 +2765,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="181" dataDxfId="180">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}" name="Table2" displayName="Table2" ref="A1:O19" totalsRowShown="0" headerRowDxfId="210" dataDxfId="209">
   <autoFilter ref="A1:O19" xr:uid="{C52CB1D0-F8CA-48F0-8056-9CCCAC455E56}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="179"/>
+    <tableColumn id="1" xr3:uid="{2113B06E-D443-4840-B65C-F4FEB2CEC2A3}" name="#" dataDxfId="208"/>
     <tableColumn id="2" xr3:uid="{4B207364-C81F-4AB0-A7A1-6179ED226E0C}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="178"/>
-    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="177"/>
-    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="176"/>
-    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="175"/>
-    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="174"/>
-    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="173"/>
-    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="172"/>
-    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="171"/>
-    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="170"/>
-    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="169"/>
-    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="168"/>
-    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="167"/>
+    <tableColumn id="3" xr3:uid="{FD398D13-E122-4551-9954-5EEEAAFA78F9}" name="Throws" dataDxfId="207"/>
+    <tableColumn id="4" xr3:uid="{6697964C-697F-4942-9683-33C2141BD08F}" name="Yr" dataDxfId="206"/>
+    <tableColumn id="5" xr3:uid="{C61F0995-6162-4E82-B25A-064264D27ED7}" name="School" dataDxfId="205"/>
+    <tableColumn id="6" xr3:uid="{A4F330A8-AB8D-49AA-B1E1-F02A293F58E7}" name="ERA" dataDxfId="204"/>
+    <tableColumn id="7" xr3:uid="{5017CAB1-AEC5-4088-8D49-2079450DC59D}" name="IP" dataDxfId="203"/>
+    <tableColumn id="8" xr3:uid="{B2562E22-015B-41E5-BFB9-E49F34F01432}" name="H" dataDxfId="202"/>
+    <tableColumn id="9" xr3:uid="{76C656A5-6337-49B7-9E8B-583892C73B44}" name="R" dataDxfId="201"/>
+    <tableColumn id="10" xr3:uid="{97D6ED12-711A-4954-B4FF-C9D0FF309CDE}" name="ER" dataDxfId="200"/>
+    <tableColumn id="11" xr3:uid="{5A8FFF1B-5C32-4924-992D-59FEDD197707}" name="HR" dataDxfId="199"/>
+    <tableColumn id="12" xr3:uid="{72437261-D18E-4130-9988-DE877ACA701A}" name="BB" dataDxfId="198"/>
+    <tableColumn id="13" xr3:uid="{A860A4A7-5F07-4F43-A4BA-A75F69060419}" name="SO" dataDxfId="197"/>
+    <tableColumn id="14" xr3:uid="{1CD680D0-497B-4A2A-B0B6-09354C2B887B}" name="WHIP" dataDxfId="196"/>
     <tableColumn id="15" xr3:uid="{6F146679-03A5-4608-8323-E75FAFF903E6}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2349,45 +2789,45 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0843ECD0-6996-45AC-A9A9-494D040880A6}" name="Table2671011" displayName="Table2671011" ref="A1:L20" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0843ECD0-6996-45AC-A9A9-494D040880A6}" name="Table2671011" displayName="Table2671011" ref="A1:L20" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:L20" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{DDD953FD-5011-49C3-9230-44FD2E664EE4}" name="#" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{DDD953FD-5011-49C3-9230-44FD2E664EE4}" name="#" dataDxfId="81"/>
     <tableColumn id="2" xr3:uid="{C5B71AC5-1440-4ADE-BA98-FB907CC5B174}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{CE3006DC-DE43-451A-BE91-7DA1A81785E0}" name="Throws" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{B5E7AA9B-A56D-4805-BB36-39D375AE9533}" name="School" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{E42FD4B5-177E-4DFE-A2F5-247966E47C02}" name="ERA" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{33B5FF3A-1C37-4003-B2C4-C7CA9DF6D068}" name="IP" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{16EB2C0E-C141-4947-83DF-FAD21AE3D884}" name="H" dataDxfId="47"/>
-    <tableColumn id="10" xr3:uid="{998831EB-F6EF-4D4E-ACED-441C6839236E}" name="ER" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{56149B59-21AA-43DC-A628-D4B816C4BD8D}" name="HR" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{172AC206-5FBE-4E78-B1E1-C9DA83788B1B}" name="BB" dataDxfId="44"/>
-    <tableColumn id="13" xr3:uid="{E8C6BF8F-17A6-4CA1-B5EE-4010D8E6E237}" name="SO" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{411967A6-2B93-4978-A8B5-D67AEDB498DB}" name="Last PL Outing, NP" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{CE3006DC-DE43-451A-BE91-7DA1A81785E0}" name="Throws" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{B5E7AA9B-A56D-4805-BB36-39D375AE9533}" name="School" dataDxfId="79"/>
+    <tableColumn id="6" xr3:uid="{E42FD4B5-177E-4DFE-A2F5-247966E47C02}" name="ERA" dataDxfId="78"/>
+    <tableColumn id="7" xr3:uid="{33B5FF3A-1C37-4003-B2C4-C7CA9DF6D068}" name="IP" dataDxfId="77"/>
+    <tableColumn id="8" xr3:uid="{16EB2C0E-C141-4947-83DF-FAD21AE3D884}" name="H" dataDxfId="76"/>
+    <tableColumn id="10" xr3:uid="{998831EB-F6EF-4D4E-ACED-441C6839236E}" name="ER" dataDxfId="75"/>
+    <tableColumn id="11" xr3:uid="{56149B59-21AA-43DC-A628-D4B816C4BD8D}" name="HR" dataDxfId="74"/>
+    <tableColumn id="12" xr3:uid="{172AC206-5FBE-4E78-B1E1-C9DA83788B1B}" name="BB" dataDxfId="73"/>
+    <tableColumn id="13" xr3:uid="{E8C6BF8F-17A6-4CA1-B5EE-4010D8E6E237}" name="SO" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{411967A6-2B93-4978-A8B5-D67AEDB498DB}" name="Last PL Outing, NP" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{20B053F4-F88D-4429-AA41-68D802CD1DF8}" name="Table1458912" displayName="Table1458912" ref="A1:M19" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{20B053F4-F88D-4429-AA41-68D802CD1DF8}" name="Table1458912" displayName="Table1458912" ref="A1:M19" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
   <autoFilter ref="A1:M19" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{41FBD773-60D6-4C44-A4FB-F9B3AC2FF215}" name="#" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{41FBD773-60D6-4C44-A4FB-F9B3AC2FF215}" name="#" dataDxfId="68"/>
     <tableColumn id="2" xr3:uid="{7283EBB3-ECFD-4150-B86E-E64B8998B944}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{754D84E1-E5E5-4628-BE76-6FC3F40A499D}" name="School" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{831F66A7-878D-4156-94CB-7A6FAC523764}" name="PA" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{3415C3C4-46AA-480E-9A6C-26B96A96F229}" name="H" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{79AF8C5A-6B40-47EB-AE42-4B6470FC7335}" name="HR" dataDxfId="35"/>
-    <tableColumn id="14" xr3:uid="{7199D5C9-AF2B-4B9A-B085-659C519522A1}" name="BB" dataDxfId="34"/>
-    <tableColumn id="15" xr3:uid="{951AAA57-6EF3-4291-812C-F7231AB5B201}" name="SO" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{C58BF7E3-497D-4DA5-A7AD-A0DA6D6F35FE}" name="AVG" dataDxfId="32"/>
-    <tableColumn id="17" xr3:uid="{E7A8FCAD-07A0-4F17-BD83-CD5B529C19EF}" name="OBP" dataDxfId="31"/>
-    <tableColumn id="19" xr3:uid="{6CC324F1-66DA-48AB-8C9A-BDD8D93CC895}" name="SB" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{DE70BA46-0B42-4F84-BC0E-499D6EF099B4}" name="K%" dataDxfId="29">
+    <tableColumn id="5" xr3:uid="{754D84E1-E5E5-4628-BE76-6FC3F40A499D}" name="School" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{831F66A7-878D-4156-94CB-7A6FAC523764}" name="PA" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{3415C3C4-46AA-480E-9A6C-26B96A96F229}" name="H" dataDxfId="65"/>
+    <tableColumn id="13" xr3:uid="{79AF8C5A-6B40-47EB-AE42-4B6470FC7335}" name="HR" dataDxfId="64"/>
+    <tableColumn id="14" xr3:uid="{7199D5C9-AF2B-4B9A-B085-659C519522A1}" name="BB" dataDxfId="63"/>
+    <tableColumn id="15" xr3:uid="{951AAA57-6EF3-4291-812C-F7231AB5B201}" name="SO" dataDxfId="62"/>
+    <tableColumn id="16" xr3:uid="{C58BF7E3-497D-4DA5-A7AD-A0DA6D6F35FE}" name="AVG" dataDxfId="61"/>
+    <tableColumn id="17" xr3:uid="{E7A8FCAD-07A0-4F17-BD83-CD5B529C19EF}" name="OBP" dataDxfId="60"/>
+    <tableColumn id="19" xr3:uid="{6CC324F1-66DA-48AB-8C9A-BDD8D93CC895}" name="SB" dataDxfId="59"/>
+    <tableColumn id="3" xr3:uid="{DE70BA46-0B42-4F84-BC0E-499D6EF099B4}" name="K%" dataDxfId="58">
       <calculatedColumnFormula>Table1458912[[#This Row],[SO]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{6D28691B-C12C-444A-8445-978CAEDE2F9E}" name="BB%" dataDxfId="28" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{6D28691B-C12C-444A-8445-978CAEDE2F9E}" name="BB%" dataDxfId="57" dataCellStyle="Percent">
       <calculatedColumnFormula>Table1458912[[#This Row],[BB]]/Table1458912[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2396,76 +2836,138 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1E8C808E-02A8-46BA-AA9E-A0D655CEA28C}" name="Table267101113" displayName="Table267101113" ref="A1:L22" totalsRowShown="0" headerRowDxfId="0" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1E8C808E-02A8-46BA-AA9E-A0D655CEA28C}" name="Table267101113" displayName="Table267101113" ref="A1:L22" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:L22" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{53D3A89E-97BA-4F08-B0AD-FEE71660E94D}" name="#" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{53D3A89E-97BA-4F08-B0AD-FEE71660E94D}" name="#" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{4F0D2D19-1FA0-4730-BACA-A68D1EAF3453}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FFBBB80F-B1A8-4EC8-976C-085201346C4D}" name="Throws" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{DE2D8D5C-2C62-455D-B77C-056B3E753E69}" name="School" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{9B3DC61A-0F76-44C1-BF9D-18954F72727A}" name="ERA" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{6D73B12E-18A1-45CA-9B08-9C1F49C331A4}" name="IP" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{ED2C7A8D-0CC4-48B4-AFAD-76907FFF619F}" name="H" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{4847CBFF-7F85-4920-B0CA-AFA3CA5E9647}" name="ER" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{7A4AE25A-68AB-4E07-89DC-44175FE1658D}" name="HR" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{C3ABA9DC-4AE3-4DB8-938A-74AF7FC956A7}" name="BB" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{92CDCC4A-9682-4E76-9232-2F4E4221A30C}" name="SO" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{D07BD69A-6BC8-4751-BDE9-1EEE5F758A61}" name="Last PL Outing, NP" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{FFBBB80F-B1A8-4EC8-976C-085201346C4D}" name="Throws" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{DE2D8D5C-2C62-455D-B77C-056B3E753E69}" name="School" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{9B3DC61A-0F76-44C1-BF9D-18954F72727A}" name="ERA" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{6D73B12E-18A1-45CA-9B08-9C1F49C331A4}" name="IP" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{ED2C7A8D-0CC4-48B4-AFAD-76907FFF619F}" name="H" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{4847CBFF-7F85-4920-B0CA-AFA3CA5E9647}" name="ER" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{7A4AE25A-68AB-4E07-89DC-44175FE1658D}" name="HR" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{C3ABA9DC-4AE3-4DB8-938A-74AF7FC956A7}" name="BB" dataDxfId="46"/>
+    <tableColumn id="13" xr3:uid="{92CDCC4A-9682-4E76-9232-2F4E4221A30C}" name="SO" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{D07BD69A-6BC8-4751-BDE9-1EEE5F758A61}" name="Last PL Outing, NP" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C4498885-CE91-45F0-BBCE-FA920BC3B339}" name="Table145891214" displayName="Table145891214" ref="A1:N25" totalsRowShown="0" headerRowDxfId="1" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{C4498885-CE91-45F0-BBCE-FA920BC3B339}" name="Table145891214" displayName="Table145891214" ref="A1:N25" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42">
   <autoFilter ref="A1:N25" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{16B85A6F-BC64-43BE-A54D-1F0B342237E0}" name="#" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{16B85A6F-BC64-43BE-A54D-1F0B342237E0}" name="#" dataDxfId="41"/>
     <tableColumn id="2" xr3:uid="{BECFA166-D20C-4030-BDA2-6CBE958455B1}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{B350053F-F69C-4349-AF75-A1C7D5CD441D}" name="School" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{CF009ACA-9A74-4B56-862C-F9D66C2AF6ED}" name="PA" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{B77625E8-C799-452D-BD3B-F54240A37442}" name="H" dataDxfId="14"/>
-    <tableColumn id="13" xr3:uid="{25DA73CE-B909-4BC6-87D2-63A7D47C7794}" name="HR" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{EB22A26E-B003-438D-946C-E282A958EB33}" name="BB" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{4EBAAB28-9C02-46B5-B028-4C01FD67FBF1}" name="SO" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{51CB3843-53F2-4E57-808F-E8A84FC824BC}" name="AVG" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{0BDDFC3E-0828-4A0F-9C42-6F5E0E5B37E8}" name="OBP" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{1ED150C3-4B5D-49FA-94CA-65AA661B2BDA}" name="SB" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{5140C3F1-FD3F-4557-9157-73F8F239BD1C}" name="K%" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{B350053F-F69C-4349-AF75-A1C7D5CD441D}" name="School" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{CF009ACA-9A74-4B56-862C-F9D66C2AF6ED}" name="PA" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{B77625E8-C799-452D-BD3B-F54240A37442}" name="H" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{25DA73CE-B909-4BC6-87D2-63A7D47C7794}" name="HR" dataDxfId="37"/>
+    <tableColumn id="14" xr3:uid="{EB22A26E-B003-438D-946C-E282A958EB33}" name="BB" dataDxfId="36"/>
+    <tableColumn id="15" xr3:uid="{4EBAAB28-9C02-46B5-B028-4C01FD67FBF1}" name="SO" dataDxfId="35"/>
+    <tableColumn id="16" xr3:uid="{51CB3843-53F2-4E57-808F-E8A84FC824BC}" name="AVG" dataDxfId="34"/>
+    <tableColumn id="17" xr3:uid="{0BDDFC3E-0828-4A0F-9C42-6F5E0E5B37E8}" name="OBP" dataDxfId="33"/>
+    <tableColumn id="19" xr3:uid="{1ED150C3-4B5D-49FA-94CA-65AA661B2BDA}" name="SB" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{5140C3F1-FD3F-4557-9157-73F8F239BD1C}" name="K%" dataDxfId="31">
       <calculatedColumnFormula>Table145891214[[#This Row],[SO]]/Table145891214[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{8BAE2FE2-C84A-4386-AA69-C3A582E43681}" name="BB%" dataDxfId="6" dataCellStyle="Percent">
+    <tableColumn id="4" xr3:uid="{8BAE2FE2-C84A-4386-AA69-C3A582E43681}" name="BB%" dataDxfId="30" dataCellStyle="Percent">
       <calculatedColumnFormula>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{AB87AD4A-D692-4DED-9C8F-8D6B85C3CE7E}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{AB87AD4A-D692-4DED-9C8F-8D6B85C3CE7E}" name="Notes" dataDxfId="29"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{4F6DE8F1-1223-47B7-8404-E7E1F40E3A1B}" name="Table26710111316" displayName="Table26710111316" ref="A1:L23" totalsRowShown="0" headerRowDxfId="1" dataDxfId="14">
+  <autoFilter ref="A1:L23" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{C7A9E0AB-6858-4B91-8F13-D294BB1D95F5}" name="#" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{2376DFB7-3BE9-41CA-BC6E-DFF4E46B515B}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{27816E56-C7C3-4BA2-8BD0-5374946A59A2}" name="Throws" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{F80E7295-648B-4626-A8FA-C53FE967778B}" name="School" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{5434239A-B347-41D5-B850-06B71B875617}" name="ERA" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{94E59633-E844-4976-AB45-1B157390D08F}" name="IP" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{4DE4EF58-54F6-4029-B106-635EF40CFB6A}" name="H" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{BBE77ECE-78E4-43F4-B319-20241ADAA5A1}" name="ER" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{13CE2457-37A8-45E3-8835-2220FD013D91}" name="HR" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{EDEE1038-6CC7-45AB-B573-D282CB76C6B5}" name="BB" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{15C46774-E8FB-43F9-964B-CB973A34D6FD}" name="SO" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{6A5ACA96-03C9-46F6-A85D-E03BC61136B7}" name="Last PL Outing, NP" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{DB96DDBF-7960-4194-91E4-69F847F62B85}" name="Table16" displayName="Table16" ref="P3:Q10" totalsRowShown="0">
+  <autoFilter ref="P3:Q10" xr:uid="{DB96DDBF-7960-4194-91E4-69F847F62B85}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P4:Q10">
+    <sortCondition ref="Q3:Q10"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{EAD49DF0-20BE-4FFF-B13B-BA7015059B6C}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{8D5D285B-AB9D-4DF7-9F31-4A1866B048BF}" name="Column2" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{A618FFF1-B95F-4D98-94A9-FE0F46493BCC}" name="Table14589121415" displayName="Table14589121415" ref="A1:N25" totalsRowShown="0" headerRowDxfId="2" dataDxfId="28">
+  <autoFilter ref="A1:N25" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{5AA32B8A-C673-4DCB-8599-8A701338F849}" name="#" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{36F0BC05-90DB-496E-A6FA-96679E8EA53E}" name="Name"/>
+    <tableColumn id="5" xr3:uid="{23BC6484-7506-443C-8D90-10D5FD244490}" name="School" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DF0EEB4F-E83B-4FEF-916B-2A7A5692B64C}" name="PA" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{ADE894CE-F81B-483E-A157-8614E8BD10EA}" name="H" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{DB2C48E8-7EBB-403B-8595-A5A5A71D1FBD}" name="HR" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{7940F47F-76EB-4A12-AB73-556A6B71B3C5}" name="BB" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{F009338C-FB86-4BC7-8ACE-F6FFD2B53B21}" name="SO" dataDxfId="21"/>
+    <tableColumn id="16" xr3:uid="{A538F081-D050-4BED-AF6E-095B5B9D35E4}" name="AVG" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{5E23692C-664F-4563-B951-F96A8BF88527}" name="OBP" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{6307967C-CC89-4437-BE66-128AC77872DA}" name="SB" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{5E948896-4A74-44BD-B69F-7D3A93A51287}" name="K%" dataDxfId="17">
+      <calculatedColumnFormula>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{BFFDF286-8E95-4E85-B948-4BBB7AD4ACA5}" name="BB%" dataDxfId="16" dataCellStyle="Percent">
+      <calculatedColumnFormula>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{B40B1A2A-53CE-44EC-8DAB-9E1A8B761996}" name="Notes" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="166" dataDxfId="165">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}" name="Table1" displayName="Table1" ref="A1:T20" totalsRowShown="0" headerRowDxfId="195" dataDxfId="194">
   <autoFilter ref="A1:T20" xr:uid="{AE68F43A-A15E-4C9D-9A1E-001C9BE15D78}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="164"/>
+    <tableColumn id="1" xr3:uid="{A807147B-25A1-4C6D-967A-9214D623EF09}" name="#" dataDxfId="193"/>
     <tableColumn id="2" xr3:uid="{1E71FAB3-5F80-433A-9CF9-976B18697772}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="163"/>
-    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="162"/>
-    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="161"/>
-    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="160"/>
-    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="159"/>
-    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="158"/>
-    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="157"/>
-    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="156"/>
-    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="155"/>
-    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="154"/>
-    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="153"/>
-    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="152"/>
-    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="151"/>
-    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="150"/>
-    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="149"/>
-    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="148"/>
-    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="147"/>
+    <tableColumn id="3" xr3:uid="{4AB65E55-7844-4087-B1D0-683AAFA3C759}" name="Bats" dataDxfId="192"/>
+    <tableColumn id="4" xr3:uid="{BADC073F-CF25-4D77-9520-ADE46FAACFBA}" name="Yr" dataDxfId="191"/>
+    <tableColumn id="5" xr3:uid="{60E54A87-2D0B-4955-918A-E7BC6DAE5929}" name="School" dataDxfId="190"/>
+    <tableColumn id="6" xr3:uid="{46B95C8A-33E8-4744-AED7-835B1F7194DD}" name="Pos" dataDxfId="189"/>
+    <tableColumn id="7" xr3:uid="{F545BCD0-7D65-4A60-BFE5-12C9D7717264}" name="G" dataDxfId="188"/>
+    <tableColumn id="8" xr3:uid="{81C2AB3C-1898-466D-8441-AE796E697804}" name="PA" dataDxfId="187"/>
+    <tableColumn id="9" xr3:uid="{C168AE12-40A4-40C9-B878-33A68F3ED889}" name="AB" dataDxfId="186"/>
+    <tableColumn id="10" xr3:uid="{ACAEFA57-3346-42CC-A8C7-1B81105A8188}" name="H" dataDxfId="185"/>
+    <tableColumn id="11" xr3:uid="{42DCAF38-D37C-449D-B6FD-E5DDB5D16B65}" name="2B" dataDxfId="184"/>
+    <tableColumn id="12" xr3:uid="{C041A354-E834-4B61-A0B0-322C7ECCC7DB}" name="3B" dataDxfId="183"/>
+    <tableColumn id="13" xr3:uid="{C1223EE5-B592-42F6-AE34-2E02EB4D8E72}" name="HR" dataDxfId="182"/>
+    <tableColumn id="14" xr3:uid="{E9539F49-31C2-4798-8FD1-6AED79363262}" name="BB" dataDxfId="181"/>
+    <tableColumn id="15" xr3:uid="{73CD7619-8051-4D47-BC45-602F5504DC82}" name="SO" dataDxfId="180"/>
+    <tableColumn id="16" xr3:uid="{9C03119F-E861-4090-B9DC-2488FC578CB8}" name="AVG" dataDxfId="179"/>
+    <tableColumn id="17" xr3:uid="{A5E296DE-495F-4351-8DEF-DF21F20724CE}" name="OBP" dataDxfId="178"/>
+    <tableColumn id="18" xr3:uid="{0541E6A2-1F2B-443C-A890-04E3BD720D19}" name="SLG" dataDxfId="177"/>
+    <tableColumn id="19" xr3:uid="{469C6478-7A18-4A10-85A0-31B706DEA170}" name="SB" dataDxfId="176"/>
     <tableColumn id="20" xr3:uid="{63D55BB7-68A9-437C-9C45-35CEA0F3FE2B}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2473,26 +2975,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="146" dataDxfId="145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}" name="Table14" displayName="Table14" ref="A32:R51" totalsRowShown="0" headerRowDxfId="175" dataDxfId="174">
   <autoFilter ref="A32:R51" xr:uid="{A194183E-0828-484C-84AB-1326C7C7A2F8}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="144"/>
+    <tableColumn id="1" xr3:uid="{CA27AF70-4DB6-482C-AF51-0219C8A5B350}" name="#" dataDxfId="173"/>
     <tableColumn id="2" xr3:uid="{ABA958D3-F28A-4755-9648-E1D80184B0D4}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="143"/>
-    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="142"/>
-    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="141"/>
-    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="140"/>
-    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="139"/>
-    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="138"/>
-    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="137"/>
-    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="136"/>
-    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="135"/>
-    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="134"/>
-    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="133"/>
-    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="132"/>
-    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="131"/>
-    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="130"/>
-    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="129"/>
+    <tableColumn id="5" xr3:uid="{25EFF3F1-D132-4B8F-AFBA-E6328B06B24A}" name="School" dataDxfId="172"/>
+    <tableColumn id="6" xr3:uid="{66D99389-B3BB-497E-B0F7-654ADDB3AC20}" name="Pos" dataDxfId="171"/>
+    <tableColumn id="7" xr3:uid="{E98C5E65-F93C-4928-B0E3-DBE19339693B}" name="G" dataDxfId="170"/>
+    <tableColumn id="8" xr3:uid="{F5DA6FDE-3B6D-4948-9103-9259F24F659B}" name="PA" dataDxfId="169"/>
+    <tableColumn id="9" xr3:uid="{FC3D35FC-61C3-4386-80A3-43585F61494A}" name="AB" dataDxfId="168"/>
+    <tableColumn id="10" xr3:uid="{BF5B5E36-C8C0-41B1-9712-EF99F9ABDE34}" name="H" dataDxfId="167"/>
+    <tableColumn id="11" xr3:uid="{39A22E60-3632-4003-8750-75572F75BED6}" name="2B" dataDxfId="166"/>
+    <tableColumn id="12" xr3:uid="{0DC28C88-027E-4D42-9B6D-A8B4B95B0AAA}" name="3B" dataDxfId="165"/>
+    <tableColumn id="13" xr3:uid="{E1D20840-1EFD-448D-8248-4304F5FA81F9}" name="HR" dataDxfId="164"/>
+    <tableColumn id="14" xr3:uid="{DF3B6DEC-8B34-45B1-B930-80F32C9E17FD}" name="BB" dataDxfId="163"/>
+    <tableColumn id="15" xr3:uid="{0846A232-95EB-4811-8EEB-982192EC5253}" name="SO" dataDxfId="162"/>
+    <tableColumn id="16" xr3:uid="{B7ACEED8-832D-4787-91DA-3C210E3F4131}" name="AVG" dataDxfId="161"/>
+    <tableColumn id="17" xr3:uid="{6834B567-A211-474A-8AE2-88A6E0844A71}" name="OBP" dataDxfId="160"/>
+    <tableColumn id="18" xr3:uid="{B5775B3F-43E9-4FA6-B2EE-D6A98D109841}" name="SLG" dataDxfId="159"/>
+    <tableColumn id="19" xr3:uid="{C047E3E1-4B25-4311-97E7-A9DECBC55C0D}" name="SB" dataDxfId="158"/>
     <tableColumn id="20" xr3:uid="{D6FD6B3E-0891-49E1-9B8B-AEF67C143114}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2500,20 +3002,20 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="128" dataDxfId="127">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}" name="Table26" displayName="Table26" ref="A1:L19" totalsRowShown="0" headerRowDxfId="157" dataDxfId="156">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="126"/>
+    <tableColumn id="1" xr3:uid="{C705151A-EB74-4BA8-83A4-516F877B946B}" name="#" dataDxfId="155"/>
     <tableColumn id="2" xr3:uid="{516EEF33-51BA-4936-98F6-F4E8C86D9AB9}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="125"/>
-    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="124"/>
-    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="123"/>
-    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="122"/>
-    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="121"/>
-    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="118"/>
-    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="117"/>
+    <tableColumn id="3" xr3:uid="{FF966585-4A70-491F-8307-2DD541F4E1BF}" name="Throws" dataDxfId="154"/>
+    <tableColumn id="5" xr3:uid="{EEED81E5-6F38-4498-BFE6-3A1D2482B5C5}" name="School" dataDxfId="153"/>
+    <tableColumn id="6" xr3:uid="{FF3727FC-8241-41BB-ABF6-87870BA22C10}" name="ERA" dataDxfId="152"/>
+    <tableColumn id="7" xr3:uid="{32D0A0F6-5B49-41C9-B83B-DECE3CB7351C}" name="IP" dataDxfId="151"/>
+    <tableColumn id="8" xr3:uid="{D3E9AC06-6878-4A94-8A45-518352D85B54}" name="H" dataDxfId="150"/>
+    <tableColumn id="10" xr3:uid="{F1EA2CB1-F6F5-44E9-A590-321C258CBD74}" name="ER" dataDxfId="149"/>
+    <tableColumn id="11" xr3:uid="{532EFB59-6B5C-4EA8-AE30-6467A2EE61BF}" name="HR" dataDxfId="148"/>
+    <tableColumn id="12" xr3:uid="{8DE32B06-4640-4ADA-AD0F-DF879B30655F}" name="BB" dataDxfId="147"/>
+    <tableColumn id="13" xr3:uid="{3A8AFCE0-D180-472B-952C-8DA2C2AA6F28}" name="SO" dataDxfId="146"/>
     <tableColumn id="15" xr3:uid="{2568029A-6AFC-43E6-B446-46528B9915F4}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2521,20 +3023,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="116" dataDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}" name="Table145" displayName="Table145" ref="A1:L20" totalsRowShown="0" headerRowDxfId="145" dataDxfId="144">
   <autoFilter ref="A1:L20" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="114"/>
+    <tableColumn id="1" xr3:uid="{09BF9663-CCDE-425B-8331-5F524943E73F}" name="#" dataDxfId="143"/>
     <tableColumn id="2" xr3:uid="{984187B9-FA1E-4DBC-B804-6E035D1B61A2}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="113"/>
-    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="112"/>
-    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="110"/>
-    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="109"/>
-    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="108"/>
-    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="107"/>
-    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="106"/>
-    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{A824BF61-8582-4F3A-8740-C41D27A0B88A}" name="School" dataDxfId="142"/>
+    <tableColumn id="8" xr3:uid="{AC2C2476-9F4E-461A-9512-05276B2647D5}" name="PA" dataDxfId="141"/>
+    <tableColumn id="10" xr3:uid="{9B72FE2D-208B-4EAB-BC92-90DDAE5CF0ED}" name="H" dataDxfId="140"/>
+    <tableColumn id="13" xr3:uid="{4D09E9CC-0D65-4711-80D1-396C4F7B9361}" name="HR" dataDxfId="139"/>
+    <tableColumn id="14" xr3:uid="{AB0A77E0-D98D-4112-91BE-8A01C0D76E04}" name="BB" dataDxfId="138"/>
+    <tableColumn id="15" xr3:uid="{1F675B20-D77B-4218-9AD7-39B4C21C720F}" name="SO" dataDxfId="137"/>
+    <tableColumn id="16" xr3:uid="{321CD5DB-937C-47C5-A553-933CF6DEAFE2}" name="AVG" dataDxfId="136"/>
+    <tableColumn id="17" xr3:uid="{E6D8B5A8-4E73-4FE4-82B8-9F6CE4636A9A}" name="OBP" dataDxfId="135"/>
+    <tableColumn id="19" xr3:uid="{5B1F5A2D-289A-47C0-AD92-CCAA342A2BD6}" name="SB" dataDxfId="134"/>
     <tableColumn id="20" xr3:uid="{9348918D-5ECB-448B-A085-487540424189}" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2542,82 +3044,82 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{50DAA861-D311-4FEC-B376-C1CD3166E88E}" name="Table267" displayName="Table267" ref="A1:K19" totalsRowShown="0" headerRowDxfId="133" dataDxfId="132">
   <autoFilter ref="A1:K19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="102"/>
+    <tableColumn id="1" xr3:uid="{23937C6B-8CD2-4A15-AD9F-7C0E5FBB9517}" name="#" dataDxfId="131"/>
     <tableColumn id="2" xr3:uid="{FD907DA6-0C2B-490D-862C-004A3C98FA20}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="101"/>
-    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="99"/>
-    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="98"/>
-    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="97"/>
-    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="95"/>
-    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="94"/>
-    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{29D109BB-BCD1-4B8C-8127-1CCDC787D7CE}" name="Throws" dataDxfId="130"/>
+    <tableColumn id="5" xr3:uid="{4A5A1796-3E02-433C-B8CB-3D23DC52CAFA}" name="School" dataDxfId="129"/>
+    <tableColumn id="6" xr3:uid="{8130B6C3-E41C-459C-8847-D6B0F77D69B7}" name="ERA" dataDxfId="128"/>
+    <tableColumn id="7" xr3:uid="{71CFCB8D-512A-47E3-B2BE-DE25556A599D}" name="IP" dataDxfId="127"/>
+    <tableColumn id="8" xr3:uid="{F8A96C65-FA9E-463B-82B7-789FD28DD3C2}" name="H" dataDxfId="126"/>
+    <tableColumn id="10" xr3:uid="{A6D8729F-9A9E-416D-A0DF-E172DA65B3DE}" name="ER" dataDxfId="125"/>
+    <tableColumn id="11" xr3:uid="{889587AF-07D7-4433-9929-AE3240751FC5}" name="HR" dataDxfId="124"/>
+    <tableColumn id="12" xr3:uid="{4A5963E4-6996-488F-943F-8DFA4E1E96B7}" name="BB" dataDxfId="123"/>
+    <tableColumn id="13" xr3:uid="{7E28BF5F-F019-4246-8289-842515022A1E}" name="SO" dataDxfId="122"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F1E385F-869A-406C-9527-2246A5108D79}" name="Table1458" displayName="Table1458" ref="A1:K17" totalsRowShown="0" headerRowDxfId="121" dataDxfId="120">
   <autoFilter ref="A1:K17" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{F275463E-1817-4676-AEAA-2C608233C375}" name="#" dataDxfId="119"/>
     <tableColumn id="2" xr3:uid="{A108195E-3469-4ACD-AA5B-AAB9CB14C59B}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="89"/>
-    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="87"/>
-    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="86"/>
-    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="85"/>
-    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="84"/>
-    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="83"/>
-    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="82"/>
-    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="81"/>
+    <tableColumn id="5" xr3:uid="{FD96D196-1E7E-4825-B86B-DBE516962EAD}" name="School" dataDxfId="118"/>
+    <tableColumn id="8" xr3:uid="{EBCF8D69-A4C6-48CE-BC63-D5AE95A34D02}" name="PA" dataDxfId="117"/>
+    <tableColumn id="10" xr3:uid="{2DBC0279-C7BD-438A-826B-0CAD410B35C2}" name="H" dataDxfId="116"/>
+    <tableColumn id="13" xr3:uid="{9D1037EA-511C-4C8E-BA83-596EBF39BB43}" name="HR" dataDxfId="115"/>
+    <tableColumn id="14" xr3:uid="{3B00CF9A-4E03-4404-915B-0E00DFCD5A78}" name="BB" dataDxfId="114"/>
+    <tableColumn id="15" xr3:uid="{872D8561-24D3-41B7-B49E-CDC9DA7C548B}" name="SO" dataDxfId="113"/>
+    <tableColumn id="16" xr3:uid="{97939727-9A9D-4BF2-995A-DFE9C816BB76}" name="AVG" dataDxfId="112"/>
+    <tableColumn id="17" xr3:uid="{AF5F757C-F32B-42F9-B262-F34120FDAD69}" name="OBP" dataDxfId="111"/>
+    <tableColumn id="19" xr3:uid="{AFABD7A1-5420-410E-AD42-3F632E6EB2BE}" name="SB" dataDxfId="110"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{4D56302D-D923-4698-847B-95A970B15BC4}" name="Table26710" displayName="Table26710" ref="A1:L19" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108">
   <autoFilter ref="A1:L19" xr:uid="{4955B4BB-3624-48AC-92A0-E9DE9F7C9A46}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="78"/>
+    <tableColumn id="1" xr3:uid="{326CE291-A42A-4B91-A365-33C45CFE3580}" name="#" dataDxfId="107"/>
     <tableColumn id="2" xr3:uid="{6377AB1F-C5EE-4699-A482-9F1094364D72}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="77"/>
-    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="76"/>
-    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="75"/>
-    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="74"/>
-    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="70"/>
-    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{B8FFCC63-0DE9-4940-86A1-5ECA254D0777}" name="Throws" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{4BCB389D-9C3D-41D8-BF40-7CA848916946}" name="School" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{F2968992-435E-4005-BFAB-95E9BDB857D2}" name="ERA" dataDxfId="104"/>
+    <tableColumn id="7" xr3:uid="{3AF954D7-3578-4C40-91D1-018BE15006E2}" name="IP" dataDxfId="103"/>
+    <tableColumn id="8" xr3:uid="{DC47FBFC-7100-4180-8A96-3D05818C10C0}" name="H" dataDxfId="102"/>
+    <tableColumn id="10" xr3:uid="{BDBB8997-50B6-4102-B31F-023633D6E864}" name="ER" dataDxfId="101"/>
+    <tableColumn id="11" xr3:uid="{2176105F-4D53-406B-A814-2DB9EC6C9356}" name="HR" dataDxfId="100"/>
+    <tableColumn id="12" xr3:uid="{AB52EAFC-765E-46D4-AFEE-2052687E4A8F}" name="BB" dataDxfId="99"/>
+    <tableColumn id="13" xr3:uid="{A9341390-C132-4BFC-AD7D-2D1195C169BD}" name="SO" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{27504B45-FC0D-472A-89AA-99FDAA388B7D}" name="Last PL Outing, NP" dataDxfId="97"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{33C0B4F1-FFFB-4E09-B5A7-33A9AA9D0CCA}" name="Table14589" displayName="Table14589" ref="A1:L15" totalsRowShown="0" headerRowDxfId="96" dataDxfId="95">
   <autoFilter ref="A1:L15" xr:uid="{14B73850-2C18-4A49-A695-35FCDB2FE39E}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{4A841F9A-BABA-49C2-8364-E1C7191E94FD}" name="#" dataDxfId="94"/>
     <tableColumn id="2" xr3:uid="{F0F04FB6-1130-4097-843F-75D32B7FDEAA}" name="Name"/>
-    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="62"/>
-    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="61"/>
-    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="60"/>
-    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="59"/>
-    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="58"/>
-    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="57"/>
-    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{6667D93F-737F-44A5-9540-25B11E9F47AA}" name="School" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{A4C539DB-251A-461E-B699-A1C35942C1F8}" name="PA" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{465E1737-0CBA-4259-B388-83AE26ACE8A7}" name="H" dataDxfId="91"/>
+    <tableColumn id="13" xr3:uid="{5AD2DEE6-FB38-4879-AAE3-65986D8F7067}" name="HR" dataDxfId="90"/>
+    <tableColumn id="14" xr3:uid="{33482F8D-4C43-4288-B33B-A264C15F3417}" name="BB" dataDxfId="89"/>
+    <tableColumn id="15" xr3:uid="{F1BEB975-858B-4E82-AD02-AC5147F965A4}" name="SO" dataDxfId="88"/>
+    <tableColumn id="16" xr3:uid="{06A1F971-C56E-4265-B81E-E09271EE864B}" name="AVG" dataDxfId="87"/>
+    <tableColumn id="17" xr3:uid="{869512D7-4ACD-49AE-8D3D-8D757B1D7545}" name="OBP" dataDxfId="86"/>
+    <tableColumn id="19" xr3:uid="{D48F2BA1-F54E-4994-8A88-BF592BDF727C}" name="SB" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{8A3C61EB-128B-4849-9414-66149D40FCE4}" name="Notes" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4567,40 +5069,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="L1" s="35" t="s">
         <v>197</v>
       </c>
     </row>
@@ -4617,7 +5119,7 @@
       <c r="D2" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="34">
         <v>13.5</v>
       </c>
       <c r="F2" s="11">
@@ -4638,7 +5140,7 @@
       <c r="K2" s="11">
         <v>4</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="1" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4655,7 +5157,7 @@
       <c r="D3" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="34">
         <v>7.12</v>
       </c>
       <c r="F3" s="11">
@@ -4676,7 +5178,7 @@
       <c r="K3" s="11">
         <v>30</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="38" t="s">
         <v>379</v>
       </c>
       <c r="P3" t="s">
@@ -4720,7 +5222,7 @@
       <c r="K4" s="1">
         <v>18</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="1" t="s">
         <v>380</v>
       </c>
       <c r="P4" t="s">
@@ -4764,7 +5266,7 @@
       <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="L5" s="34" t="s">
+      <c r="L5" s="1" t="s">
         <v>381</v>
       </c>
       <c r="P5" t="s">
@@ -4808,7 +5310,7 @@
       <c r="K6" s="1">
         <v>83</v>
       </c>
-      <c r="L6" s="34" t="s">
+      <c r="L6" s="1" t="s">
         <v>383</v>
       </c>
       <c r="P6" t="s">
@@ -4852,7 +5354,7 @@
       <c r="K7" s="1">
         <v>15</v>
       </c>
-      <c r="L7" s="34" t="s">
+      <c r="L7" s="1" t="s">
         <v>385</v>
       </c>
       <c r="P7" t="s">
@@ -4896,7 +5398,7 @@
       <c r="K8" s="1">
         <v>25</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="L8" s="1" t="s">
         <v>387</v>
       </c>
       <c r="P8" t="s">
@@ -4940,7 +5442,7 @@
       <c r="K9" s="1">
         <v>4</v>
       </c>
-      <c r="L9" s="34" t="s">
+      <c r="L9" s="1" t="s">
         <v>389</v>
       </c>
       <c r="Q9" s="23"/>
@@ -4958,7 +5460,7 @@
       <c r="D10" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <v>4.3499999999999996</v>
       </c>
       <c r="F10" s="17">
@@ -4979,7 +5481,7 @@
       <c r="K10" s="11">
         <v>38</v>
       </c>
-      <c r="L10" s="34" t="s">
+      <c r="L10" s="1" t="s">
         <v>193</v>
       </c>
       <c r="Q10" s="23"/>
@@ -5018,7 +5520,7 @@
       <c r="K11" s="1">
         <v>54</v>
       </c>
-      <c r="L11" s="34" t="s">
+      <c r="L11" s="1" t="s">
         <v>391</v>
       </c>
       <c r="Q11" s="23"/>
@@ -5057,7 +5559,7 @@
       <c r="K12" s="1">
         <v>7</v>
       </c>
-      <c r="L12" s="34" t="s">
+      <c r="L12" s="1" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5095,7 +5597,7 @@
       <c r="K13" s="1">
         <v>23</v>
       </c>
-      <c r="L13" s="34" t="s">
+      <c r="L13" s="1" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5188,7 +5690,7 @@
       <c r="D16" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="34">
         <v>5.67</v>
       </c>
       <c r="F16" s="17">
@@ -5209,7 +5711,7 @@
       <c r="K16" s="11">
         <v>50</v>
       </c>
-      <c r="L16" s="34" t="s">
+      <c r="L16" s="1" t="s">
         <v>193</v>
       </c>
     </row>
@@ -5247,7 +5749,7 @@
       <c r="K17" s="1">
         <v>53</v>
       </c>
-      <c r="L17" s="34" t="s">
+      <c r="L17" s="1" t="s">
         <v>401</v>
       </c>
     </row>
@@ -5285,7 +5787,7 @@
       <c r="K18" s="1">
         <v>4</v>
       </c>
-      <c r="L18" s="34" t="s">
+      <c r="L18" s="1" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5323,7 +5825,7 @@
       <c r="K19" s="1">
         <v>7</v>
       </c>
-      <c r="L19" s="34" t="s">
+      <c r="L19" s="1" t="s">
         <v>404</v>
       </c>
     </row>
@@ -5464,46 +5966,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="L1" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="M1" s="36" t="s">
+      <c r="M1" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="N1" s="36" t="s">
+      <c r="N1" s="35" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6552,6 +7054,1906 @@
       <c r="M25" s="33">
         <f>Table145891214[[#This Row],[BB]]/Table145891214[[#This Row],[PA]]</f>
         <v>0.1171875</v>
+      </c>
+      <c r="N25" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D56903-7E16-422D-82CE-73AAFB950DF6}">
+  <dimension ref="A1:Q23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E2" s="34">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="F2" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G2" s="11">
+        <v>9</v>
+      </c>
+      <c r="H2" s="11">
+        <v>6</v>
+      </c>
+      <c r="I2" s="11">
+        <v>1</v>
+      </c>
+      <c r="J2" s="11">
+        <v>13</v>
+      </c>
+      <c r="K2" s="11">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E3" s="34">
+        <v>9.89</v>
+      </c>
+      <c r="F3" s="11">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="G3" s="11">
+        <v>49</v>
+      </c>
+      <c r="H3" s="11">
+        <v>44</v>
+      </c>
+      <c r="I3" s="11">
+        <v>9</v>
+      </c>
+      <c r="J3" s="11">
+        <v>20</v>
+      </c>
+      <c r="K3" s="11">
+        <v>15</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>418</v>
+      </c>
+      <c r="P3" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="E4" s="5">
+        <v>6.46</v>
+      </c>
+      <c r="F4" s="17">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1">
+        <v>58</v>
+      </c>
+      <c r="H4" s="1">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1">
+        <v>39</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="P4" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>45807</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="5">
+        <v>3.66</v>
+      </c>
+      <c r="F5" s="11">
+        <v>46.2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1">
+        <v>19</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1">
+        <v>13</v>
+      </c>
+      <c r="K5" s="1">
+        <v>52</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="P5" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q5" s="23">
+        <v>45814</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="5">
+        <v>6.48</v>
+      </c>
+      <c r="F6" s="17">
+        <v>25</v>
+      </c>
+      <c r="G6" s="1">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1">
+        <v>18</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>20</v>
+      </c>
+      <c r="K6" s="1">
+        <v>33</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="P6" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>45815</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5.15</v>
+      </c>
+      <c r="F7" s="11">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="G7" s="1">
+        <v>34</v>
+      </c>
+      <c r="H7" s="1">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1">
+        <v>4</v>
+      </c>
+      <c r="J7" s="1">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1">
+        <v>41</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="P7" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q7" s="23">
+        <v>45816</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="F8" s="11">
+        <v>68.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>51</v>
+      </c>
+      <c r="H8" s="1">
+        <v>31</v>
+      </c>
+      <c r="I8" s="1">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
+        <v>74</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="P8" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q8" s="23">
+        <v>45818</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="P9" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q9" s="23">
+        <v>45819</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>443</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E10" s="34">
+        <v>9</v>
+      </c>
+      <c r="F10" s="17">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11">
+        <v>2</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="P10" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q10" s="23">
+        <v>45820</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>446</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="5">
+        <v>8</v>
+      </c>
+      <c r="F11" s="17">
+        <v>9</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>8</v>
+      </c>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q11" s="23"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3.86</v>
+      </c>
+      <c r="F12" s="11">
+        <v>18.2</v>
+      </c>
+      <c r="G12" s="1">
+        <v>16</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1">
+        <v>13</v>
+      </c>
+      <c r="K12" s="1">
+        <v>21</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>450</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="E13" s="5">
+        <v>23.73</v>
+      </c>
+      <c r="F13" s="17">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1">
+        <v>6</v>
+      </c>
+      <c r="J13" s="1">
+        <v>13</v>
+      </c>
+      <c r="K13" s="1">
+        <v>6</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>453</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E14" s="5">
+        <v>5.33</v>
+      </c>
+      <c r="F14" s="17">
+        <v>76</v>
+      </c>
+      <c r="G14" s="1">
+        <v>85</v>
+      </c>
+      <c r="H14" s="1">
+        <v>45</v>
+      </c>
+      <c r="I14" s="6">
+        <v>7</v>
+      </c>
+      <c r="J14" s="6">
+        <v>28</v>
+      </c>
+      <c r="K14" s="6">
+        <v>57</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>459</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E16" s="34">
+        <v>13.14</v>
+      </c>
+      <c r="F16" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="G16" s="11">
+        <v>24</v>
+      </c>
+      <c r="H16" s="11">
+        <v>18</v>
+      </c>
+      <c r="I16" s="11">
+        <v>3</v>
+      </c>
+      <c r="J16" s="11">
+        <v>14</v>
+      </c>
+      <c r="K16" s="11">
+        <v>16</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>468</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="5">
+        <v>11.57</v>
+      </c>
+      <c r="F17" s="11">
+        <v>2.1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1">
+        <v>4</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E18" s="5">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="F18" s="11">
+        <v>14.1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1">
+        <v>16</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2</v>
+      </c>
+      <c r="J18" s="1">
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>17</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>474</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E19" s="5">
+        <v>6.75</v>
+      </c>
+      <c r="F19" s="17">
+        <v>28</v>
+      </c>
+      <c r="G19" s="1">
+        <v>28</v>
+      </c>
+      <c r="H19" s="1">
+        <v>21</v>
+      </c>
+      <c r="I19" s="1">
+        <v>3</v>
+      </c>
+      <c r="J19" s="1">
+        <v>23</v>
+      </c>
+      <c r="K19" s="1">
+        <v>27</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>477</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E20" s="5">
+        <v>5.18</v>
+      </c>
+      <c r="F20" s="11">
+        <v>24.1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>12</v>
+      </c>
+      <c r="K20" s="1">
+        <v>27</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>480</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="F21" s="17">
+        <v>15</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>15</v>
+      </c>
+      <c r="K21" s="1">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E22" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="17">
+        <v>16</v>
+      </c>
+      <c r="G22" s="1">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1">
+        <v>8</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>9</v>
+      </c>
+      <c r="K22" s="1">
+        <v>11</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
+        <v>487</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3.24</v>
+      </c>
+      <c r="F23" s="1">
+        <v>77.2</v>
+      </c>
+      <c r="G23" s="1">
+        <v>76</v>
+      </c>
+      <c r="H23" s="1">
+        <v>28</v>
+      </c>
+      <c r="I23" s="1">
+        <v>9</v>
+      </c>
+      <c r="J23" s="1">
+        <v>21</v>
+      </c>
+      <c r="K23" s="1">
+        <v>60</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P4:Q10">
+    <sortCondition ref="P4:P10"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E8286E-F179-46C8-AC85-F5389D5F562A}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" style="29"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="14" max="14" width="42.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="M1" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="N1" s="41" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D2" s="1">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>8</v>
+      </c>
+      <c r="I2" s="27">
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="J2" s="27">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="M2" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="11">
+        <v>205</v>
+      </c>
+      <c r="E3" s="11">
+        <v>36</v>
+      </c>
+      <c r="F3" s="11">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11">
+        <v>23</v>
+      </c>
+      <c r="H3" s="11">
+        <v>59</v>
+      </c>
+      <c r="I3" s="28">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="J3" s="28">
+        <v>0.312</v>
+      </c>
+      <c r="K3" s="11">
+        <v>0</v>
+      </c>
+      <c r="L3" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.28780487804878047</v>
+      </c>
+      <c r="M3" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.11219512195121951</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>414</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="11">
+        <v>152</v>
+      </c>
+      <c r="E4" s="11">
+        <v>33</v>
+      </c>
+      <c r="F4" s="11">
+        <v>7</v>
+      </c>
+      <c r="G4" s="11">
+        <v>22</v>
+      </c>
+      <c r="H4" s="11">
+        <v>24</v>
+      </c>
+      <c r="I4" s="28">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="J4" s="28">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0</v>
+      </c>
+      <c r="L4" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="M4" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.14473684210526316</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D5" s="1">
+        <v>60</v>
+      </c>
+      <c r="E5" s="1">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1">
+        <v>18</v>
+      </c>
+      <c r="I5" s="28">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="J5" s="28">
+        <v>0.4</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
+      <c r="L5" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.3</v>
+      </c>
+      <c r="M5" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.15</v>
+      </c>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D6" s="11">
+        <v>70</v>
+      </c>
+      <c r="E6" s="11">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11">
+        <v>8</v>
+      </c>
+      <c r="H6" s="11">
+        <v>21</v>
+      </c>
+      <c r="I6" s="28">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="J6" s="28">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="K6" s="11">
+        <v>2</v>
+      </c>
+      <c r="L6" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.3</v>
+      </c>
+      <c r="M6" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.11428571428571428</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D7" s="1">
+        <v>225</v>
+      </c>
+      <c r="E7" s="1">
+        <v>64</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>23</v>
+      </c>
+      <c r="I7" s="28">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="J7" s="28">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="K7" s="6">
+        <v>3</v>
+      </c>
+      <c r="L7" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.10222222222222223</v>
+      </c>
+      <c r="M7" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>9.7777777777777783E-2</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="1">
+        <v>188</v>
+      </c>
+      <c r="E8" s="1">
+        <v>57</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="1">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1">
+        <v>36</v>
+      </c>
+      <c r="I8" s="28">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="J8" s="28">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="K8" s="6">
+        <v>10</v>
+      </c>
+      <c r="L8" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.19148936170212766</v>
+      </c>
+      <c r="M8" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>6.9148936170212769E-2</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D9" s="11">
+        <v>69</v>
+      </c>
+      <c r="E9" s="11">
+        <v>8</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <v>17</v>
+      </c>
+      <c r="H9" s="11">
+        <v>22</v>
+      </c>
+      <c r="I9" s="28">
+        <v>0.157</v>
+      </c>
+      <c r="J9" s="28">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0</v>
+      </c>
+      <c r="L9" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.3188405797101449</v>
+      </c>
+      <c r="M9" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.24637681159420291</v>
+      </c>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>445</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="D10" s="1">
+        <v>124</v>
+      </c>
+      <c r="E10" s="1">
+        <v>27</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>26</v>
+      </c>
+      <c r="I10" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="J10" s="28">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="K10" s="6">
+        <v>6</v>
+      </c>
+      <c r="L10" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.20967741935483872</v>
+      </c>
+      <c r="M10" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>7.2580645161290328E-2</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>452</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>455</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D12" s="11">
+        <v>107</v>
+      </c>
+      <c r="E12" s="11">
+        <v>27</v>
+      </c>
+      <c r="F12" s="11">
+        <v>2</v>
+      </c>
+      <c r="G12" s="11">
+        <v>7</v>
+      </c>
+      <c r="H12" s="11">
+        <v>40</v>
+      </c>
+      <c r="I12" s="28">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="J12" s="28">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="K12" s="11">
+        <v>5</v>
+      </c>
+      <c r="L12" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.37383177570093457</v>
+      </c>
+      <c r="M12" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>6.5420560747663545E-2</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>457</v>
+      </c>
+      <c r="C13" t="s">
+        <v>458</v>
+      </c>
+      <c r="D13" s="11">
+        <f>156+32+2+2+11</f>
+        <v>203</v>
+      </c>
+      <c r="E13" s="11">
+        <v>41</v>
+      </c>
+      <c r="F13" s="11">
+        <v>5</v>
+      </c>
+      <c r="G13" s="11">
+        <v>32</v>
+      </c>
+      <c r="H13" s="11">
+        <v>53</v>
+      </c>
+      <c r="I13" s="28">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="J13" s="28">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K13" s="11">
+        <v>6</v>
+      </c>
+      <c r="L13" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.26108374384236455</v>
+      </c>
+      <c r="M13" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.15763546798029557</v>
+      </c>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>462</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D14" s="11">
+        <v>136</v>
+      </c>
+      <c r="E14" s="11">
+        <v>32</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1</v>
+      </c>
+      <c r="G14" s="11">
+        <v>16</v>
+      </c>
+      <c r="H14" s="11">
+        <v>23</v>
+      </c>
+      <c r="I14" s="28">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="J14" s="28">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="K14" s="11">
+        <v>11</v>
+      </c>
+      <c r="L14" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.16911764705882354</v>
+      </c>
+      <c r="M14" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="D15" s="1">
+        <v>274</v>
+      </c>
+      <c r="E15" s="1">
+        <v>82</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1">
+        <v>23</v>
+      </c>
+      <c r="H15" s="1">
+        <v>34</v>
+      </c>
+      <c r="I15" s="28">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="J15" s="28">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="K15" s="6">
+        <v>4</v>
+      </c>
+      <c r="L15" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.12408759124087591</v>
+      </c>
+      <c r="M15" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>8.3941605839416053E-2</v>
+      </c>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>472</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="D16" s="1">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3</v>
+      </c>
+      <c r="I16" s="28">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="J16" s="28">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="M16" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
+        <v>484</v>
+      </c>
+      <c r="C17" t="s">
+        <v>485</v>
+      </c>
+      <c r="D17" s="11">
+        <v>34</v>
+      </c>
+      <c r="E17" s="11">
+        <v>6</v>
+      </c>
+      <c r="F17" s="11">
+        <v>2</v>
+      </c>
+      <c r="G17" s="11">
+        <v>3</v>
+      </c>
+      <c r="H17" s="11">
+        <v>14</v>
+      </c>
+      <c r="I17" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="J17" s="28">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="1">
+        <v>163</v>
+      </c>
+      <c r="E18" s="1">
+        <v>36</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2</v>
+      </c>
+      <c r="G18" s="1">
+        <v>21</v>
+      </c>
+      <c r="H18" s="1">
+        <v>48</v>
+      </c>
+      <c r="I18" s="28">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="J18" s="28">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="K18" s="6">
+        <v>3</v>
+      </c>
+      <c r="L18" s="32">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.29447852760736198</v>
+      </c>
+      <c r="M18" s="33">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>0.12883435582822086</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C19" s="9"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M19" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C20" s="9"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M20" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C21" s="9"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M21" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C22" s="9"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M22" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C23" s="9"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M23" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C24" s="9"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M24" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C25" s="9"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="32" t="e">
+        <f>Table14589121415[[#This Row],[SO]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M25" s="33" t="e">
+        <f>Table14589121415[[#This Row],[BB]]/Table14589121415[[#This Row],[PA]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N25" s="1"/>
     </row>
